--- a/lorenzo-playwright-kdf/excelFramework/testcases/Problems/LSTP_Problems_WF001.xlsx
+++ b/lorenzo-playwright-kdf/excelFramework/testcases/Problems/LSTP_Problems_WF001.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mkashetti\ORBIS PAS UKI-LZO\ORBIS PAS UKI-LZO\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\Problems\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0691A9C2-2A55-41AB-A581-A4F6A040C8EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E06F64E3-6808-4575-A357-2F06A8726B36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{BE3DF6D1-393A-4573-8176-869B7BDB99D6}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BE3DF6D1-393A-4573-8176-869B7BDB99D6}"/>
   </bookViews>
   <sheets>
     <sheet name="TestExecution" sheetId="1" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="897" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="875" uniqueCount="432">
   <si>
     <t>StepNo</t>
   </si>
@@ -192,6 +192,9 @@
     <t>pageEPRView</t>
   </si>
   <si>
+    <t>exists</t>
+  </si>
+  <si>
     <t>equal</t>
   </si>
   <si>
@@ -216,6 +219,9 @@
     <t>Wait for Record Procedure form to load</t>
   </si>
   <si>
+    <t>pagefrmProRecordProcedure</t>
+  </si>
+  <si>
     <t>Click Find icon to search for procedure name</t>
   </si>
   <si>
@@ -246,12 +252,21 @@
     <t>btn_Add</t>
   </si>
   <si>
+    <t>Wait for procedure to be added</t>
+  </si>
+  <si>
     <t>Click Finish Now to save the procedure record</t>
   </si>
   <si>
     <t>btn_Finishnow</t>
   </si>
   <si>
+    <t>Wait for procedure to be saved and EPR view to reload</t>
+  </si>
+  <si>
+    <t>Validate procedure details are stored by verifying Procedures and Interventions tab exists</t>
+  </si>
+  <si>
     <t>-- NAVIGATE TO HEALTH ISSUES EPR TAB AND RECORD PROBLEMS --</t>
   </si>
   <si>
@@ -264,6 +279,9 @@
     <t>Wait for Health Issues section to load</t>
   </si>
   <si>
+    <t>pageHistoryTab</t>
+  </si>
+  <si>
     <t>Click Problems tab within Health Issues section</t>
   </si>
   <si>
@@ -285,6 +303,9 @@
     <t>Wait for Problem Details form to load</t>
   </si>
   <si>
+    <t>pageDetails Tab</t>
+  </si>
+  <si>
     <t>Select Problem 1 Type</t>
   </si>
   <si>
@@ -333,6 +354,9 @@
     <t>Wait for Problem 1 to be saved</t>
   </si>
   <si>
+    <t>Validate Problem 1 is displayed in the Problems list with Active status</t>
+  </si>
+  <si>
     <t>-- RECORD PROBLEM 2 --</t>
   </si>
   <si>
@@ -372,24 +396,36 @@
     <t>Wait for Problem 2 to be saved</t>
   </si>
   <si>
+    <t>Validate Problem 2 is displayed in the Problems list with Active status</t>
+  </si>
+  <si>
     <t>-- MARK PROBLEM 1 AS MAIN PROBLEM --</t>
   </si>
   <si>
     <t>Right-click Problem 1 in Problems list to open context menu</t>
   </si>
   <si>
+    <t>rightClickElement</t>
+  </si>
+  <si>
     <t>Wait for context menu to appear</t>
   </si>
   <si>
     <t>Click Mark as Main Problem from context menu</t>
   </si>
   <si>
+    <t>page</t>
+  </si>
+  <si>
     <t>lnk_MarkasMainProblem</t>
   </si>
   <si>
     <t>Wait for scope selector to load after marking as main problem</t>
   </si>
   <si>
+    <t>pageScope SFS</t>
+  </si>
+  <si>
     <t>Validate main problem icon is displayed correctly in scope selector</t>
   </si>
   <si>
@@ -429,6 +465,9 @@
     <t>img_ExpandRow</t>
   </si>
   <si>
+    <t>Select the Episode scope row</t>
+  </si>
+  <si>
     <t>chk_Selectrow</t>
   </si>
   <si>
@@ -444,6 +483,9 @@
     <t>Wait for Problem 2 encounter update to be saved</t>
   </si>
   <si>
+    <t>Validate Problem 2 encounter change by verifying Problems tab exists</t>
+  </si>
+  <si>
     <t>-- CHANGE PROBLEM 2 STATUS TO INACTIVE --</t>
   </si>
   <si>
@@ -495,9 +537,15 @@
     <t>Wait for inactive problems to be displayed</t>
   </si>
   <si>
+    <t>Validate Problem 2 Inactive status by verifying inactive problems checkbox is active</t>
+  </si>
+  <si>
     <t>-- LINK PROCEDURE TO PROBLEM 1 --</t>
   </si>
   <si>
+    <t>Right-click Problem 1 in Problems list to open context menu for linking</t>
+  </si>
+  <si>
     <t>Click Link option from context menu to link procedure to Problem 1</t>
   </si>
   <si>
@@ -507,6 +555,9 @@
     <t>Wait for Link Problem form to load</t>
   </si>
   <si>
+    <t>pageLink problem</t>
+  </si>
+  <si>
     <t>Select Care Record Type to link</t>
   </si>
   <si>
@@ -534,6 +585,12 @@
     <t>-- STRIKEOUT PROBLEM 1 --</t>
   </si>
   <si>
+    <t>Double-click Problem 1 to open in edit mode for strikeout</t>
+  </si>
+  <si>
+    <t>Wait for Problem 1 details form to open</t>
+  </si>
+  <si>
     <t>Click Status tab to navigate to status change section</t>
   </si>
   <si>
@@ -555,6 +612,9 @@
     <t>Wait for struck-out problems to be displayed</t>
   </si>
   <si>
+    <t>Validate strikeout icons and status by verifying inactive problems are displayed</t>
+  </si>
+  <si>
     <t>-- LOGOUT --</t>
   </si>
   <si>
@@ -570,6 +630,9 @@
     <t>txt_Yes</t>
   </si>
   <si>
+    <t>Wait for login page to confirm successful logout</t>
+  </si>
+  <si>
     <t>LS1 1AA</t>
   </si>
   <si>
@@ -606,9 +669,15 @@
     <t>Inactive</t>
   </si>
   <si>
+    <t>Resolved</t>
+  </si>
+  <si>
     <t>Procedure</t>
   </si>
   <si>
+    <t>Struck Out</t>
+  </si>
+  <si>
     <t>Key</t>
   </si>
   <si>
@@ -1279,99 +1348,6 @@
   </si>
   <si>
     <t>Phrase match</t>
-  </si>
-  <si>
-    <t>Validate Problem 1 is displayed in the Problem name</t>
-  </si>
-  <si>
-    <t>Validate Problem 1 is displayed in the Problem Active status</t>
-  </si>
-  <si>
-    <t>Active</t>
-  </si>
-  <si>
-    <t>lbl_Problems1</t>
-  </si>
-  <si>
-    <t>lbl_ProblemStatus1</t>
-  </si>
-  <si>
-    <t>Validate Problem 2 is displayed in the Problem name</t>
-  </si>
-  <si>
-    <t>Validate Problem 2 is displayed in the Problem Active status</t>
-  </si>
-  <si>
-    <t>lbl_Problems2</t>
-  </si>
-  <si>
-    <t>lbl_ProblemStatus2</t>
-  </si>
-  <si>
-    <t>ClickElement</t>
-  </si>
-  <si>
-    <t>Uncheck the Scope checkbox</t>
-  </si>
-  <si>
-    <t>Deselect the Episode scope row</t>
-  </si>
-  <si>
-    <t>Store Scope of Problem 2</t>
-  </si>
-  <si>
-    <t>lbl_ProblemScope2</t>
-  </si>
-  <si>
-    <t>_ProblemScope</t>
-  </si>
-  <si>
-    <t>Validate Problem 2 scope is changed</t>
-  </si>
-  <si>
-    <t>notequal</t>
-  </si>
-  <si>
-    <t>Problem no longer relevant</t>
-  </si>
-  <si>
-    <t>pageLinkProblem</t>
-  </si>
-  <si>
-    <t>Right click Problem 1 in Problems list to open context menu for linking</t>
-  </si>
-  <si>
-    <t>Click on Link icon of Problem1</t>
-  </si>
-  <si>
-    <t>lbl_Link</t>
-  </si>
-  <si>
-    <t>lbl_LinkProcedure</t>
-  </si>
-  <si>
-    <t>Strikeout</t>
-  </si>
-  <si>
-    <t>Select Problem2</t>
-  </si>
-  <si>
-    <t>Wait for Problem 2 details to load</t>
-  </si>
-  <si>
-    <t>Validate Problem 2 is displayed in the Problem Strikeout status</t>
-  </si>
-  <si>
-    <t>btn_PrbOk</t>
-  </si>
-  <si>
-    <t>clickTab</t>
-  </si>
-  <si>
-    <t>chk_StrikeoutProblems</t>
-  </si>
-  <si>
-    <t>rClickElement</t>
   </si>
 </sst>
 </file>
@@ -1485,6 +1461,9 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1501,7 +1480,6 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1992,69 +1970,69 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED13D89B-E932-4955-85A4-923D6A664298}">
-  <dimension ref="A1:K191"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:K189"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.6328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="61.36328125" customWidth="1"/>
-    <col min="3" max="3" width="19.6328125" customWidth="1"/>
-    <col min="4" max="4" width="26.6328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.36328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="61.28515625" customWidth="1"/>
+    <col min="3" max="3" width="19.7109375" customWidth="1"/>
+    <col min="4" max="4" width="26.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.54296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="41.54296875" customWidth="1"/>
-    <col min="11" max="11" width="23.6328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="41.5703125" customWidth="1"/>
+    <col min="11" max="11" width="23.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J1" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="K1" s="11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>232</v>
+        <v>255</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>11</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>233</v>
+        <v>256</v>
       </c>
       <c r="E2" s="5"/>
       <c r="F2" s="5" t="s">
@@ -2068,18 +2046,18 @@
       </c>
       <c r="K2" s="5"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>234</v>
+        <v>257</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>11</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>235</v>
+        <v>258</v>
       </c>
       <c r="E3" s="5"/>
       <c r="F3" s="5" t="s">
@@ -2089,22 +2067,22 @@
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
       <c r="J3" s="5" t="s">
-        <v>236</v>
+        <v>259</v>
       </c>
       <c r="K3" s="5"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>237</v>
+        <v>260</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>238</v>
+        <v>261</v>
       </c>
       <c r="E4" s="5"/>
       <c r="F4" s="5" t="s">
@@ -2116,18 +2094,18 @@
       <c r="J4" s="5"/>
       <c r="K4" s="5"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>270</v>
+        <v>293</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>271</v>
+        <v>294</v>
       </c>
       <c r="E5" s="5"/>
       <c r="F5" s="5" t="s">
@@ -2139,21 +2117,21 @@
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>272</v>
+        <v>295</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>273</v>
+        <v>296</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>274</v>
+        <v>297</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>15</v>
@@ -2164,18 +2142,18 @@
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>275</v>
+        <v>298</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>276</v>
+        <v>299</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>277</v>
+        <v>300</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5" t="s">
@@ -2187,21 +2165,21 @@
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>278</v>
+        <v>301</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>276</v>
+        <v>299</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>279</v>
+        <v>302</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>280</v>
+        <v>303</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>15</v>
@@ -2212,18 +2190,18 @@
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>281</v>
+        <v>304</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>276</v>
+        <v>299</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>282</v>
+        <v>305</v>
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="5" t="s">
@@ -2235,22 +2213,22 @@
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>283</v>
+        <v>306</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>276</v>
+        <v>299</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>284</v>
+        <v>307</v>
       </c>
       <c r="E10" s="5"/>
       <c r="F10" s="5" t="s">
-        <v>285</v>
+        <v>308</v>
       </c>
       <c r="G10" s="5"/>
       <c r="H10" s="5"/>
@@ -2258,21 +2236,21 @@
       <c r="J10" s="5"/>
       <c r="K10" s="5"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>286</v>
+        <v>309</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>12</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>287</v>
+        <v>310</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>288</v>
+        <v>311</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>15</v>
@@ -2283,42 +2261,42 @@
       <c r="J11" s="5"/>
       <c r="K11" s="5"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>289</v>
+        <v>312</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>241</v>
+        <v>264</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>290</v>
+        <v>313</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>290</v>
+        <v>313</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>291</v>
+        <v>314</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>290</v>
+        <v>313</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>290</v>
+        <v>313</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>290</v>
+        <v>313</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>290</v>
+        <v>313</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>12</v>
       </c>
@@ -2326,7 +2304,7 @@
         <v>16</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>241</v>
+        <v>264</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="5"/>
@@ -2341,15 +2319,15 @@
       </c>
       <c r="K13" s="5"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>13</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>239</v>
+        <v>262</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>241</v>
+        <v>264</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="6"/>
@@ -2360,19 +2338,19 @@
       <c r="H14" s="7"/>
       <c r="I14" s="7"/>
       <c r="J14" s="7" t="s">
-        <v>240</v>
+        <v>263</v>
       </c>
       <c r="K14" s="5"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>14</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>242</v>
+        <v>265</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>241</v>
+        <v>264</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>19</v>
@@ -2389,18 +2367,18 @@
       </c>
       <c r="K15" s="5"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>243</v>
+        <v>266</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>241</v>
+        <v>264</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>244</v>
+        <v>267</v>
       </c>
       <c r="E16" s="5"/>
       <c r="F16" s="5" t="s">
@@ -2410,19 +2388,19 @@
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
       <c r="J16" s="5" t="s">
-        <v>245</v>
+        <v>268</v>
       </c>
       <c r="K16" s="5"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>246</v>
+        <v>269</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>241</v>
+        <v>264</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>24</v>
@@ -2435,22 +2413,22 @@
       <c r="H17" s="5"/>
       <c r="I17" s="5"/>
       <c r="J17" s="5" t="s">
-        <v>247</v>
+        <v>270</v>
       </c>
       <c r="K17" s="5"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>248</v>
+        <v>271</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>241</v>
+        <v>264</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>249</v>
+        <v>272</v>
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="5" t="s">
@@ -2462,18 +2440,18 @@
       <c r="J18" s="5"/>
       <c r="K18" s="5"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>250</v>
+        <v>273</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>241</v>
+        <v>264</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>249</v>
+        <v>272</v>
       </c>
       <c r="E19" s="5"/>
       <c r="F19" s="5" t="s">
@@ -2483,19 +2461,19 @@
       <c r="H19" s="5"/>
       <c r="I19" s="5"/>
       <c r="J19" s="8" t="s">
-        <v>251</v>
+        <v>274</v>
       </c>
       <c r="K19" s="5"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>252</v>
+        <v>275</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>241</v>
+        <v>264</v>
       </c>
       <c r="D20" s="5" t="s">
         <v>22</v>
@@ -2510,18 +2488,18 @@
       <c r="J20" s="5"/>
       <c r="K20" s="5"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>292</v>
+        <v>315</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>254</v>
+        <v>277</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>293</v>
+        <v>316</v>
       </c>
       <c r="E21" s="5"/>
       <c r="F21" s="5" t="s">
@@ -2533,18 +2511,18 @@
       <c r="J21" s="5"/>
       <c r="K21" s="5"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <v>21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>294</v>
+        <v>317</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>254</v>
+        <v>277</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>255</v>
+        <v>278</v>
       </c>
       <c r="E22" s="5"/>
       <c r="F22" s="5" t="s">
@@ -2558,18 +2536,18 @@
         <v>27</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>22</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>295</v>
+        <v>318</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>254</v>
+        <v>277</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>256</v>
+        <v>279</v>
       </c>
       <c r="E23" s="5"/>
       <c r="F23" s="5" t="s">
@@ -2583,18 +2561,18 @@
         <v>29</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
         <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>296</v>
+        <v>319</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>254</v>
+        <v>277</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>257</v>
+        <v>280</v>
       </c>
       <c r="E24" s="5"/>
       <c r="F24" s="5" t="s">
@@ -2606,15 +2584,15 @@
       <c r="J24" s="5"/>
       <c r="K24" s="5"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>24</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>297</v>
+        <v>320</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>260</v>
+        <v>283</v>
       </c>
       <c r="D25" s="5"/>
       <c r="E25" s="5"/>
@@ -2629,18 +2607,18 @@
       </c>
       <c r="K25" s="5"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
         <v>25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>259</v>
+        <v>282</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>260</v>
+        <v>283</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>261</v>
+        <v>284</v>
       </c>
       <c r="E26" s="5"/>
       <c r="F26" s="5" t="s">
@@ -2652,15 +2630,15 @@
       <c r="J26" s="5"/>
       <c r="K26" s="5"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <v>26</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>297</v>
+        <v>320</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>260</v>
+        <v>283</v>
       </c>
       <c r="D27" s="5"/>
       <c r="E27" s="5"/>
@@ -2675,15 +2653,15 @@
       </c>
       <c r="K27" s="5"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
         <v>27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>298</v>
+        <v>321</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>260</v>
+        <v>283</v>
       </c>
       <c r="D28" s="5"/>
       <c r="E28" s="5"/>
@@ -2694,19 +2672,19 @@
       <c r="H28" s="5"/>
       <c r="I28" s="5"/>
       <c r="J28" s="5" t="s">
-        <v>253</v>
+        <v>276</v>
       </c>
       <c r="K28" s="5"/>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <v>28</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>299</v>
+        <v>322</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>260</v>
+        <v>283</v>
       </c>
       <c r="D29" s="5"/>
       <c r="E29" s="5"/>
@@ -2717,70 +2695,70 @@
       <c r="H29" s="5"/>
       <c r="I29" s="5"/>
       <c r="J29" s="5" t="s">
-        <v>262</v>
+        <v>285</v>
       </c>
       <c r="K29" s="5"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
         <v>29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>263</v>
+        <v>286</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>260</v>
+        <v>283</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>264</v>
+        <v>287</v>
       </c>
       <c r="E30" s="5"/>
       <c r="F30" s="5" t="s">
-        <v>265</v>
+        <v>288</v>
       </c>
       <c r="G30" s="5"/>
       <c r="H30" s="5"/>
       <c r="I30" s="5"/>
       <c r="J30" s="5" t="s">
-        <v>266</v>
+        <v>289</v>
       </c>
       <c r="K30" s="5"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
         <v>30</v>
       </c>
-      <c r="B31" s="9" t="s">
-        <v>267</v>
+      <c r="B31" s="10" t="s">
+        <v>290</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>260</v>
-      </c>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9" t="s">
-        <v>268</v>
-      </c>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="9"/>
-      <c r="J31" s="9" t="s">
-        <v>269</v>
+        <v>283</v>
+      </c>
+      <c r="D31" s="10"/>
+      <c r="E31" s="10"/>
+      <c r="F31" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="G31" s="10"/>
+      <c r="H31" s="10"/>
+      <c r="I31" s="10"/>
+      <c r="J31" s="10" t="s">
+        <v>292</v>
       </c>
       <c r="K31" s="5"/>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
         <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>300</v>
+        <v>323</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>301</v>
+        <v>324</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>302</v>
+        <v>325</v>
       </c>
       <c r="E32" s="5"/>
       <c r="F32" s="5" t="s">
@@ -2791,21 +2769,21 @@
       <c r="I32" s="5"/>
       <c r="J32" s="5"/>
       <c r="K32" s="5" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
         <v>32</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>304</v>
+        <v>327</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>301</v>
+        <v>324</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>305</v>
+        <v>328</v>
       </c>
       <c r="E33" s="5"/>
       <c r="F33" s="5" t="s">
@@ -2816,21 +2794,21 @@
       <c r="I33" s="5"/>
       <c r="J33" s="5"/>
       <c r="K33" s="5" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
         <v>33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>307</v>
+        <v>330</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>301</v>
+        <v>324</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>308</v>
+        <v>331</v>
       </c>
       <c r="E34" s="5"/>
       <c r="F34" s="5" t="s">
@@ -2842,15 +2820,15 @@
       <c r="J34" s="5"/>
       <c r="K34" s="5"/>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
         <v>34</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>297</v>
+        <v>320</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>301</v>
+        <v>324</v>
       </c>
       <c r="D35" s="5"/>
       <c r="E35" s="5"/>
@@ -2865,18 +2843,18 @@
       </c>
       <c r="K35" s="5"/>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
         <v>35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>309</v>
+        <v>332</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>301</v>
+        <v>324</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>310</v>
+        <v>333</v>
       </c>
       <c r="E36" s="5"/>
       <c r="F36" s="5" t="s">
@@ -2888,15 +2866,15 @@
       <c r="J36" s="5"/>
       <c r="K36" s="5"/>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
         <v>36</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>311</v>
+        <v>334</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>301</v>
+        <v>324</v>
       </c>
       <c r="D37" s="5" t="s">
         <v>33</v>
@@ -2911,15 +2889,15 @@
       <c r="J37" s="5"/>
       <c r="K37" s="5"/>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
         <v>37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>297</v>
+        <v>320</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>312</v>
+        <v>335</v>
       </c>
       <c r="D38" s="5"/>
       <c r="E38" s="5"/>
@@ -2934,18 +2912,18 @@
       </c>
       <c r="K38" s="5"/>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
         <v>38</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>313</v>
+        <v>336</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>312</v>
+        <v>335</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>314</v>
+        <v>337</v>
       </c>
       <c r="E39" s="5"/>
       <c r="F39" s="5" t="s">
@@ -2957,15 +2935,15 @@
       <c r="J39" s="5"/>
       <c r="K39" s="5"/>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
         <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>315</v>
+        <v>338</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>316</v>
+        <v>339</v>
       </c>
       <c r="D40" s="5" t="s">
         <v>43</v>
@@ -2982,15 +2960,15 @@
       </c>
       <c r="K40" s="5"/>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
         <v>40</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>317</v>
+        <v>340</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>316</v>
+        <v>339</v>
       </c>
       <c r="D41" s="5" t="s">
         <v>22</v>
@@ -3005,18 +2983,18 @@
       <c r="J41" s="5"/>
       <c r="K41" s="5"/>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" s="5">
         <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>318</v>
+        <v>341</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>316</v>
+        <v>339</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="E42" s="5"/>
       <c r="F42" s="5" t="s">
@@ -3028,18 +3006,18 @@
       <c r="J42" s="5"/>
       <c r="K42" s="5"/>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" s="5">
         <v>42</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>319</v>
+        <v>342</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>312</v>
+        <v>335</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>320</v>
+        <v>343</v>
       </c>
       <c r="E43" s="5"/>
       <c r="F43" s="5" t="s">
@@ -3050,21 +3028,21 @@
       <c r="I43" s="5"/>
       <c r="J43" s="5"/>
       <c r="K43" s="5" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" s="5">
         <v>43</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>322</v>
+        <v>345</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>312</v>
+        <v>335</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>323</v>
+        <v>346</v>
       </c>
       <c r="E44" s="5"/>
       <c r="F44" s="5" t="s">
@@ -3076,18 +3054,18 @@
       <c r="J44" s="5"/>
       <c r="K44" s="5"/>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" s="5">
         <v>44</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>324</v>
+        <v>347</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>326</v>
+        <v>349</v>
       </c>
       <c r="E45" s="5"/>
       <c r="F45" s="5" t="s">
@@ -3098,21 +3076,21 @@
       <c r="I45" s="5"/>
       <c r="J45" s="5"/>
       <c r="K45" s="5" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" s="5">
         <v>45</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>328</v>
+        <v>351</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>329</v>
+        <v>352</v>
       </c>
       <c r="E46" s="5"/>
       <c r="F46" s="5" t="s">
@@ -3123,21 +3101,21 @@
       <c r="I46" s="5"/>
       <c r="J46" s="5"/>
       <c r="K46" s="5" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" s="5">
         <v>46</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>331</v>
+        <v>354</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>332</v>
+        <v>355</v>
       </c>
       <c r="E47" s="5"/>
       <c r="F47" s="5" t="s">
@@ -3148,21 +3126,21 @@
       <c r="I47" s="5"/>
       <c r="J47" s="5"/>
       <c r="K47" s="5" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" s="5">
         <v>47</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>334</v>
+        <v>357</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>335</v>
+        <v>358</v>
       </c>
       <c r="E48" s="5"/>
       <c r="F48" s="5" t="s">
@@ -3173,42 +3151,42 @@
       <c r="I48" s="5"/>
       <c r="J48" s="5"/>
       <c r="K48" s="5" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="5">
         <v>48</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>337</v>
+        <v>360</v>
       </c>
       <c r="C49" s="5"/>
       <c r="D49" s="5"/>
       <c r="E49" s="5"/>
       <c r="F49" s="5" t="s">
-        <v>338</v>
+        <v>361</v>
       </c>
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
       <c r="I49" s="5"/>
       <c r="J49" s="5" t="s">
-        <v>339</v>
+        <v>362</v>
       </c>
       <c r="K49" s="5"/>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" s="5">
         <v>49</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>340</v>
+        <v>363</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>341</v>
+        <v>364</v>
       </c>
       <c r="E50" s="5"/>
       <c r="F50" s="5" t="s">
@@ -3218,22 +3196,22 @@
       <c r="H50" s="5"/>
       <c r="I50" s="5"/>
       <c r="J50" s="5" t="s">
-        <v>342</v>
+        <v>365</v>
       </c>
       <c r="K50" s="5"/>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" s="5">
         <v>50</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>343</v>
+        <v>366</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>344</v>
+        <v>367</v>
       </c>
       <c r="E51" s="5"/>
       <c r="F51" s="5" t="s">
@@ -3243,22 +3221,22 @@
       <c r="H51" s="5"/>
       <c r="I51" s="5"/>
       <c r="J51" s="5" t="s">
-        <v>342</v>
+        <v>365</v>
       </c>
       <c r="K51" s="5"/>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" s="5">
         <v>51</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>345</v>
+        <v>368</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>346</v>
+        <v>369</v>
       </c>
       <c r="E52" s="5"/>
       <c r="F52" s="5" t="s">
@@ -3268,22 +3246,22 @@
       <c r="H52" s="5"/>
       <c r="I52" s="5"/>
       <c r="J52" s="5" t="s">
-        <v>347</v>
+        <v>370</v>
       </c>
       <c r="K52" s="5"/>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" s="5">
         <v>52</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>313</v>
+        <v>336</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>314</v>
+        <v>337</v>
       </c>
       <c r="E53" s="5"/>
       <c r="F53" s="5" t="s">
@@ -3295,15 +3273,15 @@
       <c r="J53" s="5"/>
       <c r="K53" s="5"/>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" s="5">
         <v>53</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>315</v>
+        <v>338</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>348</v>
+        <v>371</v>
       </c>
       <c r="D54" s="5" t="s">
         <v>43</v>
@@ -3315,20 +3293,20 @@
       <c r="G54" s="5"/>
       <c r="H54" s="5"/>
       <c r="I54" s="5"/>
-      <c r="J54" s="11" t="s">
-        <v>349</v>
+      <c r="J54" s="12" t="s">
+        <v>372</v>
       </c>
       <c r="K54" s="5"/>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" s="5">
         <v>54</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>317</v>
+        <v>340</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>348</v>
+        <v>371</v>
       </c>
       <c r="D55" s="5" t="s">
         <v>22</v>
@@ -3343,18 +3321,18 @@
       <c r="J55" s="5"/>
       <c r="K55" s="5"/>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" s="5">
         <v>55</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>318</v>
+        <v>341</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>348</v>
+        <v>371</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="E56" s="5"/>
       <c r="F56" s="5" t="s">
@@ -3366,18 +3344,18 @@
       <c r="J56" s="5"/>
       <c r="K56" s="5"/>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" s="5">
         <v>56</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>350</v>
+        <v>373</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>260</v>
+        <v>283</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E57" s="5"/>
       <c r="F57" s="5" t="s">
@@ -3389,15 +3367,15 @@
       <c r="J57" s="5"/>
       <c r="K57" s="5"/>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" s="5">
         <v>57</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>297</v>
+        <v>320</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>260</v>
+        <v>283</v>
       </c>
       <c r="D58" s="5"/>
       <c r="E58" s="5"/>
@@ -3412,39 +3390,39 @@
       </c>
       <c r="K58" s="5"/>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" s="5">
         <v>58</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>337</v>
+        <v>360</v>
       </c>
       <c r="C59" s="5"/>
       <c r="D59" s="5"/>
       <c r="E59" s="5"/>
       <c r="F59" s="5" t="s">
-        <v>338</v>
+        <v>361</v>
       </c>
       <c r="G59" s="5"/>
       <c r="H59" s="5"/>
       <c r="I59" s="5"/>
       <c r="J59" s="5" t="s">
-        <v>339</v>
+        <v>362</v>
       </c>
       <c r="K59" s="5"/>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" s="5">
         <v>59</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>351</v>
+        <v>374</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>352</v>
+        <v>375</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>353</v>
+        <v>376</v>
       </c>
       <c r="E60" s="5"/>
       <c r="F60" s="5" t="s">
@@ -3454,19 +3432,19 @@
       <c r="H60" s="5"/>
       <c r="I60" s="5"/>
       <c r="J60" s="5" t="s">
-        <v>342</v>
+        <v>365</v>
       </c>
       <c r="K60" s="5"/>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" s="5">
         <v>60</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>297</v>
+        <v>320</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>352</v>
+        <v>375</v>
       </c>
       <c r="D61" s="5"/>
       <c r="E61" s="5"/>
@@ -3481,18 +3459,18 @@
       </c>
       <c r="K61" s="5"/>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" s="5">
         <v>61</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>354</v>
+        <v>377</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>352</v>
+        <v>375</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>355</v>
+        <v>378</v>
       </c>
       <c r="E62" s="5"/>
       <c r="F62" s="5" t="s">
@@ -3504,15 +3482,15 @@
       <c r="J62" s="5"/>
       <c r="K62" s="5"/>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" s="5">
         <v>62</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>297</v>
+        <v>320</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>260</v>
+        <v>283</v>
       </c>
       <c r="D63" s="5"/>
       <c r="E63" s="5"/>
@@ -3525,38 +3503,38 @@
       <c r="J63" s="5"/>
       <c r="K63" s="5"/>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" s="5">
         <v>63</v>
       </c>
-      <c r="B64" s="12" t="s">
-        <v>356</v>
-      </c>
-      <c r="C64" s="12" t="s">
-        <v>260</v>
-      </c>
-      <c r="D64" s="12" t="s">
-        <v>257</v>
-      </c>
-      <c r="E64" s="12"/>
-      <c r="F64" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="G64" s="12"/>
-      <c r="H64" s="12"/>
-      <c r="I64" s="12"/>
-      <c r="J64" s="12"/>
+      <c r="B64" s="13" t="s">
+        <v>379</v>
+      </c>
+      <c r="C64" s="13" t="s">
+        <v>283</v>
+      </c>
+      <c r="D64" s="13" t="s">
+        <v>280</v>
+      </c>
+      <c r="E64" s="13"/>
+      <c r="F64" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G64" s="13"/>
+      <c r="H64" s="13"/>
+      <c r="I64" s="13"/>
+      <c r="J64" s="13"/>
       <c r="K64" s="5"/>
     </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" s="5">
         <v>64</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>297</v>
+        <v>320</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>276</v>
+        <v>299</v>
       </c>
       <c r="D65" s="5"/>
       <c r="E65" s="5"/>
@@ -3569,18 +3547,18 @@
       <c r="J65" s="5"/>
       <c r="K65" s="5"/>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" s="5">
         <v>65</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>357</v>
-      </c>
-      <c r="C66" s="12" t="s">
-        <v>358</v>
-      </c>
-      <c r="D66" s="13" t="s">
-        <v>284</v>
+        <v>380</v>
+      </c>
+      <c r="C66" s="13" t="s">
+        <v>381</v>
+      </c>
+      <c r="D66" s="14" t="s">
+        <v>307</v>
       </c>
       <c r="E66" s="5"/>
       <c r="F66" s="5" t="s">
@@ -3592,63 +3570,63 @@
       <c r="J66" s="5"/>
       <c r="K66" s="5"/>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" s="5">
         <v>66</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>359</v>
-      </c>
-      <c r="C67" s="12"/>
-      <c r="D67" s="13"/>
+        <v>382</v>
+      </c>
+      <c r="C67" s="13"/>
+      <c r="D67" s="14"/>
       <c r="E67" s="5"/>
       <c r="F67" s="5" t="s">
-        <v>360</v>
+        <v>383</v>
       </c>
       <c r="G67" s="5"/>
       <c r="H67" s="5"/>
       <c r="I67" s="5"/>
       <c r="J67" s="5" t="s">
-        <v>361</v>
+        <v>384</v>
       </c>
       <c r="K67" s="5"/>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" s="5">
         <v>67</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>357</v>
-      </c>
-      <c r="C68" s="12" t="s">
-        <v>358</v>
-      </c>
-      <c r="D68" s="13" t="s">
-        <v>284</v>
+        <v>380</v>
+      </c>
+      <c r="C68" s="13" t="s">
+        <v>381</v>
+      </c>
+      <c r="D68" s="14" t="s">
+        <v>307</v>
       </c>
       <c r="E68" s="5"/>
       <c r="F68" s="5" t="s">
-        <v>362</v>
+        <v>385</v>
       </c>
       <c r="G68" s="5"/>
       <c r="H68" s="5"/>
       <c r="I68" s="5" t="s">
-        <v>363</v>
+        <v>386</v>
       </c>
       <c r="J68" s="5" t="s">
-        <v>364</v>
+        <v>387</v>
       </c>
       <c r="K68" s="5"/>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" s="5">
         <v>68</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>297</v>
-      </c>
-      <c r="C69" s="12" t="s">
-        <v>358</v>
+        <v>320</v>
+      </c>
+      <c r="C69" s="13" t="s">
+        <v>381</v>
       </c>
       <c r="D69" s="5"/>
       <c r="E69" s="5"/>
@@ -3661,61 +3639,61 @@
       <c r="J69" s="5"/>
       <c r="K69" s="5"/>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" s="5">
         <v>69</v>
       </c>
-      <c r="B70" s="12" t="s">
-        <v>365</v>
-      </c>
-      <c r="C70" s="12" t="s">
-        <v>366</v>
-      </c>
-      <c r="D70" s="12" t="s">
-        <v>367</v>
-      </c>
-      <c r="E70" s="12"/>
-      <c r="F70" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="G70" s="12"/>
-      <c r="H70" s="12"/>
-      <c r="I70" s="12"/>
-      <c r="J70" s="12"/>
+      <c r="B70" s="13" t="s">
+        <v>388</v>
+      </c>
+      <c r="C70" s="13" t="s">
+        <v>389</v>
+      </c>
+      <c r="D70" s="13" t="s">
+        <v>390</v>
+      </c>
+      <c r="E70" s="13"/>
+      <c r="F70" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G70" s="13"/>
+      <c r="H70" s="13"/>
+      <c r="I70" s="13"/>
+      <c r="J70" s="13"/>
       <c r="K70" s="5"/>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" s="5">
         <v>70</v>
       </c>
-      <c r="B71" s="12" t="s">
-        <v>368</v>
-      </c>
-      <c r="C71" s="12" t="s">
-        <v>369</v>
-      </c>
-      <c r="D71" s="12" t="s">
-        <v>370</v>
-      </c>
-      <c r="E71" s="12"/>
-      <c r="F71" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="G71" s="12"/>
-      <c r="H71" s="12"/>
-      <c r="I71" s="12"/>
-      <c r="J71" s="12"/>
+      <c r="B71" s="13" t="s">
+        <v>391</v>
+      </c>
+      <c r="C71" s="13" t="s">
+        <v>392</v>
+      </c>
+      <c r="D71" s="13" t="s">
+        <v>393</v>
+      </c>
+      <c r="E71" s="13"/>
+      <c r="F71" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G71" s="13"/>
+      <c r="H71" s="13"/>
+      <c r="I71" s="13"/>
+      <c r="J71" s="13"/>
       <c r="K71" s="5"/>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A72" s="5">
         <v>71</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>297</v>
-      </c>
-      <c r="C72" s="12" t="s">
-        <v>369</v>
+        <v>320</v>
+      </c>
+      <c r="C72" s="13" t="s">
+        <v>392</v>
       </c>
       <c r="D72" s="5"/>
       <c r="E72" s="5"/>
@@ -3725,2752 +3703,2025 @@
       <c r="G72" s="5"/>
       <c r="H72" s="5"/>
       <c r="I72" s="5"/>
-      <c r="J72" s="12">
+      <c r="J72" s="13">
         <v>10</v>
       </c>
       <c r="K72" s="5"/>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A73" s="5">
         <v>72</v>
       </c>
-      <c r="B73" s="12" t="s">
-        <v>371</v>
-      </c>
-      <c r="C73" s="12" t="s">
-        <v>369</v>
-      </c>
-      <c r="D73" s="12" t="s">
-        <v>372</v>
-      </c>
-      <c r="E73" s="12"/>
-      <c r="F73" s="12" t="s">
-        <v>373</v>
-      </c>
-      <c r="G73" s="12" t="s">
-        <v>374</v>
-      </c>
-      <c r="H73" s="12" t="s">
-        <v>375</v>
-      </c>
-      <c r="I73" s="12"/>
-      <c r="J73" s="12" t="s">
-        <v>376</v>
+      <c r="B73" s="13" t="s">
+        <v>394</v>
+      </c>
+      <c r="C73" s="13" t="s">
+        <v>392</v>
+      </c>
+      <c r="D73" s="13" t="s">
+        <v>395</v>
+      </c>
+      <c r="E73" s="13"/>
+      <c r="F73" s="13" t="s">
+        <v>396</v>
+      </c>
+      <c r="G73" s="13" t="s">
+        <v>397</v>
+      </c>
+      <c r="H73" s="13" t="s">
+        <v>398</v>
+      </c>
+      <c r="I73" s="13"/>
+      <c r="J73" s="13" t="s">
+        <v>399</v>
       </c>
       <c r="K73" s="5"/>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A74" s="5">
         <v>73</v>
       </c>
-      <c r="B74" s="12" t="s">
-        <v>377</v>
-      </c>
-      <c r="C74" s="12" t="s">
+      <c r="B74" s="13" t="s">
+        <v>400</v>
+      </c>
+      <c r="C74" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="D74" s="12" t="s">
-        <v>378</v>
-      </c>
-      <c r="E74" s="12" t="s">
-        <v>379</v>
-      </c>
-      <c r="F74" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="G74" s="12"/>
-      <c r="H74" s="12"/>
-      <c r="I74" s="12"/>
-      <c r="J74" s="12"/>
+      <c r="D74" s="13" t="s">
+        <v>401</v>
+      </c>
+      <c r="E74" s="13" t="s">
+        <v>402</v>
+      </c>
+      <c r="F74" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G74" s="13"/>
+      <c r="H74" s="13"/>
+      <c r="I74" s="13"/>
+      <c r="J74" s="13"/>
       <c r="K74" s="5"/>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A75" s="5">
         <v>74</v>
       </c>
-      <c r="B75" s="12" t="s">
-        <v>380</v>
-      </c>
-      <c r="C75" s="12" t="s">
-        <v>381</v>
-      </c>
-      <c r="D75" s="12" t="s">
+      <c r="B75" s="13" t="s">
+        <v>403</v>
+      </c>
+      <c r="C75" s="13" t="s">
+        <v>404</v>
+      </c>
+      <c r="D75" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E75" s="12"/>
-      <c r="F75" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="G75" s="12"/>
-      <c r="H75" s="12"/>
-      <c r="I75" s="12"/>
-      <c r="J75" s="12"/>
+      <c r="E75" s="13"/>
+      <c r="F75" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G75" s="13"/>
+      <c r="H75" s="13"/>
+      <c r="I75" s="13"/>
+      <c r="J75" s="13"/>
       <c r="K75" s="5"/>
     </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A76" s="5">
         <v>75</v>
       </c>
-      <c r="B76" s="15" t="s">
+      <c r="B76" t="s">
         <v>44</v>
       </c>
-      <c r="C76" s="15" t="s">
+      <c r="C76" t="s">
         <v>12</v>
       </c>
-      <c r="D76" s="15"/>
-      <c r="E76" s="15"/>
-      <c r="F76" s="15" t="s">
+      <c r="F76" t="s">
         <v>13</v>
       </c>
-      <c r="G76" s="5"/>
-      <c r="H76" s="5"/>
-      <c r="I76" s="5"/>
-      <c r="J76" s="15"/>
-      <c r="K76" s="15"/>
-    </row>
-    <row r="77" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="G76" s="9"/>
+      <c r="H76" s="9"/>
+      <c r="I76" s="9"/>
+      <c r="J76">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A77" s="5">
         <v>76</v>
       </c>
-      <c r="B77" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="C77" s="15"/>
-      <c r="D77" s="15"/>
-      <c r="E77" s="15"/>
-      <c r="F77" s="15" t="s">
+      <c r="B77" t="s">
+        <v>48</v>
+      </c>
+      <c r="F77" t="s">
         <v>14</v>
       </c>
-      <c r="G77" s="15"/>
-      <c r="H77" s="15"/>
-      <c r="I77" s="15"/>
-      <c r="J77" s="15">
-        <v>1</v>
-      </c>
-      <c r="K77" s="15"/>
-    </row>
-    <row r="78" spans="1:11" x14ac:dyDescent="0.35">
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A78" s="5">
         <v>77</v>
       </c>
-      <c r="B78" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="C78" s="15" t="s">
+      <c r="B78" t="s">
+        <v>49</v>
+      </c>
+      <c r="C78" t="s">
         <v>12</v>
       </c>
-      <c r="D78" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="E78" s="15"/>
-      <c r="F78" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G78" s="15"/>
-      <c r="H78" s="15"/>
-      <c r="I78" s="15"/>
-      <c r="J78" s="15"/>
-      <c r="K78" s="15"/>
-    </row>
-    <row r="79" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="D78" t="s">
+        <v>50</v>
+      </c>
+      <c r="F78" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A79" s="5">
         <v>78</v>
       </c>
-      <c r="B79" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="C79" s="15" t="s">
+      <c r="B79" t="s">
+        <v>51</v>
+      </c>
+      <c r="C79" t="s">
         <v>12</v>
       </c>
-      <c r="D79" s="15"/>
-      <c r="E79" s="15"/>
-      <c r="F79" s="15" t="s">
+      <c r="F79" t="s">
         <v>13</v>
       </c>
-      <c r="G79" s="15"/>
-      <c r="H79" s="15"/>
-      <c r="I79" s="15"/>
-      <c r="J79" s="15"/>
-      <c r="K79" s="15"/>
-    </row>
-    <row r="80" spans="1:11" x14ac:dyDescent="0.35">
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A80" s="5">
         <v>79</v>
       </c>
-      <c r="B80" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="C80" s="15" t="s">
+      <c r="B80" t="s">
+        <v>52</v>
+      </c>
+      <c r="C80" t="s">
         <v>12</v>
       </c>
-      <c r="D80" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="E80" s="15"/>
-      <c r="F80" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G80" s="15"/>
-      <c r="H80" s="15"/>
-      <c r="I80" s="15"/>
-      <c r="J80" s="15"/>
-      <c r="K80" s="15"/>
-    </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="D80" t="s">
+        <v>53</v>
+      </c>
+      <c r="F80" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A81" s="5">
         <v>80</v>
       </c>
-      <c r="B81" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="C81" s="15" t="s">
-        <v>390</v>
-      </c>
-      <c r="D81" s="15"/>
-      <c r="E81" s="15"/>
-      <c r="F81" s="15" t="s">
+      <c r="B81" t="s">
+        <v>54</v>
+      </c>
+      <c r="C81" t="s">
+        <v>413</v>
+      </c>
+      <c r="F81" t="s">
         <v>13</v>
       </c>
-      <c r="G81" s="15"/>
-      <c r="H81" s="15"/>
-      <c r="I81" s="15"/>
-      <c r="J81" s="15"/>
-      <c r="K81" s="15"/>
-    </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.35">
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A82" s="5">
         <v>81</v>
       </c>
-      <c r="B82" s="15" t="s">
-        <v>392</v>
-      </c>
-      <c r="C82" s="15" t="s">
-        <v>390</v>
-      </c>
-      <c r="D82" s="15" t="s">
-        <v>394</v>
-      </c>
-      <c r="E82" s="15"/>
-      <c r="F82" s="15" t="s">
-        <v>265</v>
-      </c>
-      <c r="G82" s="15"/>
-      <c r="H82" s="15"/>
-      <c r="I82" s="15"/>
-      <c r="J82" s="15" t="s">
-        <v>393</v>
-      </c>
-      <c r="K82" s="15"/>
-    </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B82" t="s">
+        <v>415</v>
+      </c>
+      <c r="C82" t="s">
+        <v>413</v>
+      </c>
+      <c r="D82" t="s">
+        <v>417</v>
+      </c>
+      <c r="F82" t="s">
+        <v>288</v>
+      </c>
+      <c r="J82" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A83" s="5">
         <v>82</v>
       </c>
-      <c r="B83" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="C83" s="15" t="s">
-        <v>390</v>
-      </c>
-      <c r="D83" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="E83" s="15"/>
-      <c r="F83" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G83" s="15"/>
-      <c r="H83" s="15"/>
-      <c r="I83" s="15"/>
-      <c r="J83" s="15"/>
-      <c r="K83" s="15"/>
-    </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B83" t="s">
+        <v>56</v>
+      </c>
+      <c r="C83" t="s">
+        <v>413</v>
+      </c>
+      <c r="D83" t="s">
+        <v>57</v>
+      </c>
+      <c r="F83" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A84" s="5">
         <v>83</v>
       </c>
-      <c r="B84" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="C84" s="15" t="s">
-        <v>390</v>
-      </c>
-      <c r="D84" s="15"/>
-      <c r="E84" s="15"/>
-      <c r="F84" s="15" t="s">
+      <c r="B84" t="s">
+        <v>58</v>
+      </c>
+      <c r="C84" t="s">
+        <v>413</v>
+      </c>
+      <c r="F84" t="s">
         <v>13</v>
       </c>
-      <c r="G84" s="15"/>
-      <c r="H84" s="15"/>
-      <c r="I84" s="15"/>
-      <c r="J84" s="15"/>
-      <c r="K84" s="15"/>
-    </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.35">
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A85" s="5">
         <v>84</v>
       </c>
-      <c r="B85" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="C85" s="15" t="s">
-        <v>390</v>
-      </c>
-      <c r="D85" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="E85" s="15"/>
+      <c r="B85" t="s">
+        <v>59</v>
+      </c>
+      <c r="C85" t="s">
+        <v>413</v>
+      </c>
+      <c r="D85" t="s">
+        <v>60</v>
+      </c>
       <c r="F85" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G85" s="15"/>
-      <c r="H85" s="15"/>
-      <c r="I85" s="15"/>
-      <c r="J85" s="15"/>
-      <c r="K85" s="15" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="K85" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A86" s="5">
         <v>85</v>
       </c>
-      <c r="B86" s="15" t="s">
-        <v>403</v>
-      </c>
-      <c r="C86" s="15" t="s">
-        <v>390</v>
-      </c>
-      <c r="D86" s="15" t="s">
-        <v>407</v>
-      </c>
-      <c r="E86" s="15"/>
+      <c r="B86" t="s">
+        <v>426</v>
+      </c>
+      <c r="C86" t="s">
+        <v>413</v>
+      </c>
+      <c r="D86" t="s">
+        <v>430</v>
+      </c>
       <c r="F86" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="G86" s="15"/>
-      <c r="H86" s="15"/>
-      <c r="I86" s="15"/>
-      <c r="J86" s="15" t="s">
-        <v>408</v>
-      </c>
-      <c r="K86" s="15"/>
-    </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="J86" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A87" s="5">
         <v>86</v>
       </c>
-      <c r="B87" s="15" t="s">
-        <v>404</v>
-      </c>
-      <c r="C87" s="15" t="s">
-        <v>390</v>
-      </c>
-      <c r="D87" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="E87" s="15"/>
-      <c r="F87" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G87" s="15"/>
-      <c r="H87" s="15"/>
-      <c r="I87" s="15"/>
-      <c r="J87" s="15"/>
-      <c r="K87" s="15"/>
-    </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B87" t="s">
+        <v>427</v>
+      </c>
+      <c r="C87" t="s">
+        <v>413</v>
+      </c>
+      <c r="D87" t="s">
+        <v>62</v>
+      </c>
+      <c r="F87" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A88" s="5">
         <v>87</v>
       </c>
-      <c r="B88" s="15" t="s">
-        <v>405</v>
-      </c>
-      <c r="C88" s="15" t="s">
-        <v>390</v>
-      </c>
-      <c r="D88" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="E88" s="15"/>
-      <c r="F88" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G88" s="15"/>
-      <c r="H88" s="15"/>
-      <c r="I88" s="15"/>
-      <c r="J88" s="15"/>
-      <c r="K88" s="15"/>
-    </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B88" t="s">
+        <v>428</v>
+      </c>
+      <c r="C88" t="s">
+        <v>413</v>
+      </c>
+      <c r="D88" t="s">
+        <v>64</v>
+      </c>
+      <c r="F88" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A89" s="5">
         <v>88</v>
       </c>
-      <c r="B89" s="15" t="s">
-        <v>406</v>
-      </c>
-      <c r="C89" s="15" t="s">
-        <v>390</v>
-      </c>
-      <c r="D89" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="E89" s="15"/>
-      <c r="F89" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G89" s="15"/>
-      <c r="H89" s="15"/>
-      <c r="I89" s="15"/>
-      <c r="J89" s="15"/>
-      <c r="K89" s="15"/>
-    </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B89" t="s">
+        <v>429</v>
+      </c>
+      <c r="C89" t="s">
+        <v>413</v>
+      </c>
+      <c r="D89" t="s">
+        <v>65</v>
+      </c>
+      <c r="F89" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A90" s="5">
         <v>89</v>
       </c>
-      <c r="B90" s="15" t="s">
-        <v>391</v>
-      </c>
-      <c r="C90" s="15" t="s">
-        <v>390</v>
-      </c>
-      <c r="D90" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="E90" s="15"/>
-      <c r="F90" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G90" s="15"/>
-      <c r="H90" s="15"/>
-      <c r="I90" s="15"/>
-      <c r="J90" s="15"/>
-      <c r="K90" s="15"/>
-    </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B90" t="s">
+        <v>414</v>
+      </c>
+      <c r="C90" t="s">
+        <v>413</v>
+      </c>
+      <c r="D90" t="s">
+        <v>94</v>
+      </c>
+      <c r="F90" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A91" s="5">
         <v>90</v>
       </c>
-      <c r="B91" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="C91" s="15" t="s">
-        <v>390</v>
-      </c>
-      <c r="D91" s="15"/>
-      <c r="E91" s="15"/>
-      <c r="F91" s="15" t="s">
+      <c r="B91" t="s">
+        <v>63</v>
+      </c>
+      <c r="C91" t="s">
+        <v>413</v>
+      </c>
+      <c r="F91" t="s">
         <v>14</v>
       </c>
-      <c r="G91" s="15"/>
-      <c r="H91" s="15"/>
-      <c r="I91" s="15"/>
-      <c r="J91" s="15">
-        <v>5</v>
-      </c>
-      <c r="K91" s="15"/>
-    </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="J91">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A92" s="5">
         <v>91</v>
       </c>
-      <c r="B92" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="C92" s="15" t="s">
-        <v>390</v>
-      </c>
-      <c r="D92" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="E92" s="15"/>
-      <c r="F92" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G92" s="15"/>
-      <c r="H92" s="15"/>
-      <c r="I92" s="15"/>
-      <c r="J92" s="15"/>
-      <c r="K92" s="15"/>
-    </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B92" t="s">
+        <v>67</v>
+      </c>
+      <c r="C92" t="s">
+        <v>413</v>
+      </c>
+      <c r="D92" t="s">
+        <v>68</v>
+      </c>
+      <c r="F92" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A93" s="5">
         <v>92</v>
       </c>
-      <c r="B93" s="15" t="s">
-        <v>395</v>
-      </c>
-      <c r="C93" s="15" t="s">
+      <c r="B93" t="s">
+        <v>418</v>
+      </c>
+      <c r="C93" t="s">
         <v>12</v>
       </c>
-      <c r="D93" s="15"/>
-      <c r="E93" s="15"/>
-      <c r="F93" s="15" t="s">
+      <c r="F93" t="s">
         <v>13</v>
       </c>
-      <c r="G93" s="15"/>
-      <c r="H93" s="15"/>
-      <c r="I93" s="15"/>
-      <c r="J93" s="15"/>
-      <c r="K93" s="15"/>
-    </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.35">
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A94" s="5">
         <v>93</v>
       </c>
-      <c r="B94" s="15" t="s">
+      <c r="B94" t="s">
+        <v>420</v>
+      </c>
+      <c r="C94" t="s">
+        <v>12</v>
+      </c>
+      <c r="D94" t="s">
+        <v>419</v>
+      </c>
+      <c r="F94" t="s">
+        <v>396</v>
+      </c>
+      <c r="G94" t="s">
         <v>397</v>
       </c>
-      <c r="C94" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="D94" s="15" t="s">
-        <v>396</v>
-      </c>
-      <c r="E94" s="15"/>
-      <c r="F94" s="15" t="s">
-        <v>373</v>
-      </c>
-      <c r="G94" s="15" t="s">
-        <v>374</v>
-      </c>
-      <c r="H94" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="I94" s="15"/>
-      <c r="J94" s="15"/>
-      <c r="K94" s="15" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="H94" t="s">
+        <v>47</v>
+      </c>
+      <c r="K94" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A95" s="5">
         <v>94</v>
       </c>
-      <c r="B95" s="15" t="s">
-        <v>398</v>
-      </c>
-      <c r="C95" s="15" t="s">
+      <c r="B95" t="s">
+        <v>421</v>
+      </c>
+      <c r="C95" t="s">
         <v>12</v>
       </c>
-      <c r="D95" s="15" t="s">
-        <v>400</v>
-      </c>
-      <c r="E95" s="15"/>
-      <c r="F95" s="15" t="s">
-        <v>373</v>
-      </c>
-      <c r="G95" s="15" t="s">
-        <v>374</v>
-      </c>
-      <c r="H95" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="I95" s="15"/>
-      <c r="J95" s="15" t="s">
-        <v>402</v>
-      </c>
-      <c r="K95" s="15"/>
-    </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="D95" t="s">
+        <v>423</v>
+      </c>
+      <c r="F95" t="s">
+        <v>396</v>
+      </c>
+      <c r="G95" t="s">
+        <v>397</v>
+      </c>
+      <c r="H95" t="s">
+        <v>47</v>
+      </c>
+      <c r="J95" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A96" s="5">
         <v>95</v>
       </c>
-      <c r="B96" s="15" t="s">
-        <v>399</v>
-      </c>
-      <c r="C96" s="15" t="s">
+      <c r="B96" t="s">
+        <v>422</v>
+      </c>
+      <c r="C96" t="s">
         <v>12</v>
       </c>
-      <c r="D96" s="15" t="s">
-        <v>401</v>
-      </c>
-      <c r="E96" s="15"/>
-      <c r="F96" s="15" t="s">
-        <v>373</v>
-      </c>
-      <c r="G96" s="15" t="s">
-        <v>374</v>
-      </c>
-      <c r="H96" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="I96" s="15"/>
-      <c r="J96" s="15" t="s">
-        <v>393</v>
-      </c>
-      <c r="K96" s="15"/>
-    </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="D96" t="s">
+        <v>424</v>
+      </c>
+      <c r="F96" t="s">
+        <v>396</v>
+      </c>
+      <c r="G96" t="s">
+        <v>397</v>
+      </c>
+      <c r="H96" t="s">
+        <v>47</v>
+      </c>
+      <c r="J96" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" s="5">
         <v>96</v>
       </c>
-      <c r="B97" s="15" t="s">
+      <c r="B97" t="s">
         <v>66</v>
       </c>
-      <c r="C97" s="15"/>
-      <c r="D97" s="15"/>
-      <c r="E97" s="15"/>
-      <c r="F97" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="G97" s="15"/>
-      <c r="H97" s="15"/>
-      <c r="I97" s="15"/>
-      <c r="J97" s="15"/>
-      <c r="K97" s="15"/>
-    </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C97" t="s">
+        <v>55</v>
+      </c>
+      <c r="F97" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" s="5">
         <v>97</v>
       </c>
-      <c r="B98" s="15" t="s">
+      <c r="B98" t="s">
         <v>67</v>
       </c>
-      <c r="C98" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="D98" s="15" t="s">
+      <c r="C98" t="s">
+        <v>55</v>
+      </c>
+      <c r="D98" t="s">
         <v>68</v>
       </c>
-      <c r="E98" s="15"/>
-      <c r="F98" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G98" s="15"/>
-      <c r="H98" s="15"/>
-      <c r="I98" s="15"/>
-      <c r="J98" s="15"/>
-      <c r="K98" s="15"/>
-    </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="F98" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" s="5">
         <v>98</v>
       </c>
-      <c r="B99" s="15" t="s">
+      <c r="B99" t="s">
         <v>69</v>
       </c>
-      <c r="C99" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D99" s="15"/>
-      <c r="E99" s="15"/>
-      <c r="F99" s="15" t="s">
+      <c r="C99" t="s">
+        <v>45</v>
+      </c>
+      <c r="F99" t="s">
         <v>13</v>
       </c>
-      <c r="G99" s="15"/>
-      <c r="H99" s="15"/>
-      <c r="I99" s="15"/>
-      <c r="J99" s="15"/>
-      <c r="K99" s="15"/>
-    </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="J99" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" s="5">
         <v>99</v>
       </c>
-      <c r="B100" s="15" t="s">
+      <c r="B100" t="s">
         <v>70</v>
       </c>
-      <c r="C100" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D100" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="E100" s="15"/>
-      <c r="F100" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G100" s="15"/>
-      <c r="H100" s="15"/>
-      <c r="I100" s="15"/>
-      <c r="J100" s="15"/>
-      <c r="K100" s="15"/>
-    </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C100" t="s">
+        <v>45</v>
+      </c>
+      <c r="D100" t="s">
+        <v>50</v>
+      </c>
+      <c r="F100" t="s">
+        <v>42</v>
+      </c>
+      <c r="G100" t="s">
+        <v>46</v>
+      </c>
+      <c r="H100" t="s">
+        <v>47</v>
+      </c>
+      <c r="J100">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" s="5">
         <v>100</v>
       </c>
-      <c r="B101" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="C101" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D101" s="15"/>
-      <c r="E101" s="15"/>
-      <c r="F101" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G101" s="15"/>
-      <c r="H101" s="15"/>
-      <c r="I101" s="15"/>
-      <c r="J101" s="15">
-        <v>1</v>
-      </c>
-      <c r="K101" s="15"/>
-    </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B101" t="s">
+        <v>71</v>
+      </c>
+      <c r="F101" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" s="5">
         <v>101</v>
       </c>
-      <c r="B102" s="15" t="s">
+      <c r="B102" t="s">
+        <v>72</v>
+      </c>
+      <c r="C102" t="s">
+        <v>45</v>
+      </c>
+      <c r="D102" t="s">
         <v>73</v>
       </c>
-      <c r="C102" s="15"/>
-      <c r="D102" s="15"/>
-      <c r="E102" s="15"/>
-      <c r="F102" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="G102" s="15"/>
-      <c r="H102" s="15"/>
-      <c r="I102" s="15"/>
-      <c r="J102" s="15"/>
-      <c r="K102" s="15"/>
-    </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="F102" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" s="5">
         <v>102</v>
       </c>
-      <c r="B103" s="15" t="s">
+      <c r="B103" t="s">
         <v>74</v>
       </c>
-      <c r="C103" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D103" s="15" t="s">
+      <c r="C103" t="s">
         <v>75</v>
       </c>
-      <c r="E103" s="15"/>
-      <c r="F103" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G103" s="15"/>
-      <c r="H103" s="15"/>
-      <c r="I103" s="15"/>
-      <c r="J103" s="15"/>
-      <c r="K103" s="15"/>
-    </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="F103" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" s="5">
         <v>103</v>
       </c>
-      <c r="B104" s="15" t="s">
+      <c r="B104" t="s">
         <v>76</v>
       </c>
-      <c r="C104" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D104" s="15"/>
-      <c r="E104" s="15"/>
-      <c r="F104" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G104" s="15"/>
-      <c r="H104" s="15"/>
-      <c r="I104" s="15"/>
-      <c r="J104" s="15"/>
-      <c r="K104" s="15"/>
-    </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C104" t="s">
+        <v>75</v>
+      </c>
+      <c r="D104" t="s">
+        <v>77</v>
+      </c>
+      <c r="F104" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" s="5">
         <v>104</v>
       </c>
-      <c r="B105" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="C105" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D105" s="15" t="s">
+      <c r="B105" t="s">
         <v>78</v>
       </c>
-      <c r="E105" s="15"/>
-      <c r="F105" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="G105" s="15"/>
-      <c r="H105" s="15"/>
-      <c r="I105" s="15"/>
-      <c r="J105" s="15"/>
-      <c r="K105" s="15" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C105" t="s">
+        <v>75</v>
+      </c>
+      <c r="F105" t="s">
+        <v>13</v>
+      </c>
+      <c r="J105">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" s="5">
         <v>105</v>
       </c>
-      <c r="B106" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="C106" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D106" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="E106" s="15"/>
-      <c r="F106" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G106" s="15"/>
-      <c r="H106" s="15"/>
-      <c r="I106" s="15"/>
-      <c r="J106" s="15"/>
-      <c r="K106" s="15"/>
-    </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B106" t="s">
+        <v>79</v>
+      </c>
+      <c r="F106" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" s="5">
         <v>106</v>
       </c>
-      <c r="B107" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="C107" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D107" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="E107" s="15"/>
-      <c r="F107" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="G107" s="15"/>
-      <c r="H107" s="15"/>
-      <c r="I107" s="15"/>
-      <c r="J107" s="15"/>
-      <c r="K107" s="15" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B107" t="s">
+        <v>80</v>
+      </c>
+      <c r="C107" t="s">
+        <v>75</v>
+      </c>
+      <c r="D107" t="s">
+        <v>81</v>
+      </c>
+      <c r="F107" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" s="5">
         <v>107</v>
       </c>
-      <c r="B108" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="C108" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D108" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="E108" s="15"/>
-      <c r="F108" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G108" s="15"/>
-      <c r="H108" s="15"/>
-      <c r="I108" s="15"/>
-      <c r="J108" s="15"/>
-      <c r="K108" s="15"/>
-    </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B108" t="s">
+        <v>82</v>
+      </c>
+      <c r="C108" t="s">
+        <v>83</v>
+      </c>
+      <c r="F108" t="s">
+        <v>13</v>
+      </c>
+      <c r="K108" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" s="5">
         <v>108</v>
       </c>
-      <c r="B109" s="15" t="s">
+      <c r="B109" t="s">
+        <v>84</v>
+      </c>
+      <c r="C109" t="s">
+        <v>83</v>
+      </c>
+      <c r="D109" t="s">
         <v>85</v>
       </c>
-      <c r="C109" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D109" s="15"/>
-      <c r="E109" s="15"/>
-      <c r="F109" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G109" s="15"/>
-      <c r="H109" s="15"/>
-      <c r="I109" s="15"/>
-      <c r="J109" s="15"/>
-      <c r="K109" s="15"/>
-    </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="F109" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A110" s="5">
         <v>109</v>
       </c>
-      <c r="B110" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="C110" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D110" s="15" t="s">
-        <v>436</v>
-      </c>
-      <c r="E110" s="15"/>
-      <c r="F110" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G110" s="15"/>
-      <c r="H110" s="15"/>
-      <c r="I110" s="15"/>
-      <c r="J110" s="15"/>
-      <c r="K110" s="15"/>
-    </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B110" t="s">
+        <v>87</v>
+      </c>
+      <c r="C110" t="s">
+        <v>83</v>
+      </c>
+      <c r="D110" t="s">
+        <v>88</v>
+      </c>
+      <c r="F110" t="s">
+        <v>15</v>
+      </c>
+      <c r="K110" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A111" s="5">
         <v>110</v>
       </c>
-      <c r="B111" s="15" t="s">
-        <v>88</v>
-      </c>
-      <c r="C111" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D111" s="15" t="s">
+      <c r="B111" t="s">
         <v>89</v>
       </c>
-      <c r="E111" s="15"/>
-      <c r="F111" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G111" s="15"/>
-      <c r="H111" s="15"/>
-      <c r="I111" s="15"/>
-      <c r="J111" s="15"/>
-      <c r="K111" s="15"/>
-    </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C111" t="s">
+        <v>83</v>
+      </c>
+      <c r="D111" t="s">
+        <v>60</v>
+      </c>
+      <c r="F111" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" s="5">
         <v>111</v>
       </c>
-      <c r="B112" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="C112" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D112" s="15" t="s">
+      <c r="B112" t="s">
         <v>91</v>
       </c>
-      <c r="E112" s="15"/>
-      <c r="F112" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G112" s="15"/>
-      <c r="H112" s="15"/>
-      <c r="I112" s="15"/>
-      <c r="J112" s="15"/>
-      <c r="K112" s="15"/>
-    </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="C112" t="s">
+        <v>83</v>
+      </c>
+      <c r="D112" t="s">
+        <v>62</v>
+      </c>
+      <c r="F112" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A113" s="5">
         <v>112</v>
       </c>
-      <c r="B113" s="15" t="s">
+      <c r="B113" t="s">
         <v>92</v>
       </c>
-      <c r="C113" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D113" s="15"/>
-      <c r="E113" s="15"/>
-      <c r="F113" s="15" t="s">
+      <c r="C113" t="s">
+        <v>83</v>
+      </c>
+      <c r="F113" t="s">
         <v>13</v>
       </c>
-      <c r="G113" s="15"/>
-      <c r="H113" s="15"/>
-      <c r="I113" s="15"/>
-      <c r="J113" s="15"/>
-      <c r="K113" s="15"/>
-    </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.35">
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A114" s="5">
         <v>113</v>
       </c>
-      <c r="B114" s="15" t="s">
-        <v>409</v>
-      </c>
-      <c r="C114" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D114" s="15" t="s">
-        <v>412</v>
-      </c>
-      <c r="E114" s="15"/>
-      <c r="F114" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="G114" s="15" t="s">
-        <v>374</v>
-      </c>
-      <c r="H114" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="I114" s="15"/>
-      <c r="J114" s="15"/>
-      <c r="K114" s="15" t="s">
+      <c r="B114" t="s">
+        <v>93</v>
+      </c>
+      <c r="C114" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="D114" t="s">
+        <v>94</v>
+      </c>
+      <c r="F114" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A115" s="5">
         <v>114</v>
       </c>
-      <c r="B115" s="15" t="s">
-        <v>410</v>
-      </c>
-      <c r="C115" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D115" s="15" t="s">
-        <v>413</v>
-      </c>
-      <c r="E115" s="15"/>
-      <c r="F115" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="G115" s="15" t="s">
-        <v>374</v>
-      </c>
-      <c r="H115" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="I115" s="15"/>
-      <c r="J115" s="15" t="s">
-        <v>411</v>
-      </c>
-      <c r="K115" s="15"/>
-    </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B115" t="s">
+        <v>95</v>
+      </c>
+      <c r="C115" t="s">
+        <v>83</v>
+      </c>
+      <c r="D115" t="s">
+        <v>96</v>
+      </c>
+      <c r="F115" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A116" s="5">
         <v>115</v>
       </c>
-      <c r="B116" s="15" t="s">
-        <v>93</v>
-      </c>
-      <c r="C116" s="15"/>
-      <c r="D116" s="15"/>
-      <c r="E116" s="15"/>
-      <c r="F116" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="G116" s="15"/>
-      <c r="H116" s="15"/>
-      <c r="I116" s="15"/>
-      <c r="J116" s="15">
-        <v>1</v>
-      </c>
-      <c r="K116" s="15"/>
-    </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B116" t="s">
+        <v>97</v>
+      </c>
+      <c r="C116" t="s">
+        <v>83</v>
+      </c>
+      <c r="D116" t="s">
+        <v>98</v>
+      </c>
+      <c r="F116" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A117" s="5">
         <v>116</v>
       </c>
-      <c r="B117" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="C117" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D117" s="15" t="s">
+      <c r="B117" t="s">
+        <v>99</v>
+      </c>
+      <c r="C117" t="s">
         <v>75</v>
       </c>
-      <c r="E117" s="15"/>
-      <c r="F117" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G117" s="15"/>
-      <c r="H117" s="15"/>
-      <c r="I117" s="15"/>
-      <c r="J117" s="15"/>
-      <c r="K117" s="15"/>
-    </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="F117" t="s">
+        <v>13</v>
+      </c>
+      <c r="J117" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A118" s="5">
         <v>117</v>
       </c>
-      <c r="B118" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="C118" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D118" s="15"/>
-      <c r="E118" s="15"/>
-      <c r="F118" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G118" s="15"/>
-      <c r="H118" s="15"/>
-      <c r="I118" s="15"/>
-      <c r="J118" s="15"/>
-      <c r="K118" s="15"/>
-    </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B118" t="s">
+        <v>100</v>
+      </c>
+      <c r="C118" t="s">
+        <v>75</v>
+      </c>
+      <c r="D118" t="s">
+        <v>77</v>
+      </c>
+      <c r="F118" t="s">
+        <v>42</v>
+      </c>
+      <c r="G118" t="s">
+        <v>46</v>
+      </c>
+      <c r="H118" t="s">
+        <v>47</v>
+      </c>
+      <c r="J118">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A119" s="5">
         <v>118</v>
       </c>
-      <c r="B119" s="15" t="s">
-        <v>95</v>
-      </c>
-      <c r="C119" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D119" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="E119" s="15"/>
-      <c r="F119" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="G119" s="15"/>
-      <c r="H119" s="15"/>
-      <c r="I119" s="15"/>
-      <c r="J119" s="15"/>
-      <c r="K119" s="15" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B119" t="s">
+        <v>101</v>
+      </c>
+      <c r="F119" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A120" s="5">
         <v>119</v>
       </c>
-      <c r="B120" s="15" t="s">
-        <v>97</v>
-      </c>
-      <c r="C120" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D120" s="15" t="s">
+      <c r="B120" t="s">
+        <v>102</v>
+      </c>
+      <c r="C120" t="s">
+        <v>75</v>
+      </c>
+      <c r="D120" t="s">
         <v>81</v>
       </c>
-      <c r="E120" s="15"/>
-      <c r="F120" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G120" s="15"/>
-      <c r="H120" s="15"/>
-      <c r="I120" s="15"/>
-      <c r="J120" s="15"/>
-      <c r="K120" s="15"/>
-    </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="F120" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A121" s="5">
         <v>120</v>
       </c>
-      <c r="B121" s="15" t="s">
-        <v>98</v>
-      </c>
-      <c r="C121" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D121" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="E121" s="15"/>
-      <c r="F121" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="G121" s="15"/>
-      <c r="H121" s="15"/>
-      <c r="I121" s="15"/>
-      <c r="J121" s="15"/>
-      <c r="K121" s="15" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B121" t="s">
+        <v>82</v>
+      </c>
+      <c r="C121" t="s">
+        <v>83</v>
+      </c>
+      <c r="F121" t="s">
+        <v>13</v>
+      </c>
+      <c r="K121" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A122" s="5">
         <v>121</v>
       </c>
-      <c r="B122" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="C122" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D122" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="E122" s="15"/>
-      <c r="F122" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G122" s="15"/>
-      <c r="H122" s="15"/>
-      <c r="I122" s="15"/>
-      <c r="J122" s="15"/>
-      <c r="K122" s="15"/>
-    </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B122" t="s">
+        <v>103</v>
+      </c>
+      <c r="C122" t="s">
+        <v>83</v>
+      </c>
+      <c r="D122" t="s">
+        <v>85</v>
+      </c>
+      <c r="F122" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A123" s="5">
         <v>122</v>
       </c>
-      <c r="B123" s="15" t="s">
-        <v>101</v>
-      </c>
-      <c r="C123" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D123" s="15"/>
-      <c r="E123" s="15"/>
-      <c r="F123" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G123" s="15"/>
-      <c r="H123" s="15"/>
-      <c r="I123" s="15"/>
-      <c r="J123" s="15"/>
-      <c r="K123" s="15"/>
-    </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B123" t="s">
+        <v>105</v>
+      </c>
+      <c r="C123" t="s">
+        <v>83</v>
+      </c>
+      <c r="D123" t="s">
+        <v>88</v>
+      </c>
+      <c r="F123" t="s">
+        <v>15</v>
+      </c>
+      <c r="K123" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A124" s="5">
         <v>123</v>
       </c>
-      <c r="B124" s="15" t="s">
-        <v>102</v>
-      </c>
-      <c r="C124" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D124" s="15" t="s">
-        <v>436</v>
-      </c>
-      <c r="E124" s="15"/>
-      <c r="F124" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G124" s="15"/>
-      <c r="H124" s="15"/>
-      <c r="I124" s="15"/>
-      <c r="J124" s="15"/>
-      <c r="K124" s="15"/>
-    </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B124" t="s">
+        <v>106</v>
+      </c>
+      <c r="C124" t="s">
+        <v>83</v>
+      </c>
+      <c r="D124" t="s">
+        <v>60</v>
+      </c>
+      <c r="F124" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A125" s="5">
         <v>124</v>
       </c>
-      <c r="B125" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="C125" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D125" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="E125" s="15"/>
-      <c r="F125" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G125" s="15"/>
-      <c r="H125" s="15"/>
-      <c r="I125" s="15"/>
-      <c r="J125" s="15"/>
-      <c r="K125" s="15"/>
-    </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B125" t="s">
+        <v>108</v>
+      </c>
+      <c r="C125" t="s">
+        <v>83</v>
+      </c>
+      <c r="D125" t="s">
+        <v>62</v>
+      </c>
+      <c r="F125" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A126" s="5">
         <v>125</v>
       </c>
-      <c r="B126" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="C126" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D126" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="E126" s="15"/>
-      <c r="F126" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G126" s="15"/>
-      <c r="H126" s="15"/>
-      <c r="I126" s="15"/>
-      <c r="J126" s="15"/>
-      <c r="K126" s="15"/>
-    </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B126" t="s">
+        <v>109</v>
+      </c>
+      <c r="C126" t="s">
+        <v>83</v>
+      </c>
+      <c r="F126" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A127" s="5">
         <v>126</v>
       </c>
-      <c r="B127" s="15" t="s">
-        <v>105</v>
-      </c>
-      <c r="C127" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D127" s="15"/>
-      <c r="E127" s="15"/>
-      <c r="F127" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G127" s="15"/>
-      <c r="H127" s="15"/>
-      <c r="I127" s="15"/>
-      <c r="J127" s="15"/>
-      <c r="K127" s="15"/>
-    </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B127" t="s">
+        <v>110</v>
+      </c>
+      <c r="C127" t="s">
+        <v>83</v>
+      </c>
+      <c r="D127" t="s">
+        <v>94</v>
+      </c>
+      <c r="F127" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A128" s="5">
         <v>127</v>
       </c>
-      <c r="B128" s="15" t="s">
-        <v>414</v>
-      </c>
-      <c r="C128" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D128" s="15" t="s">
-        <v>416</v>
-      </c>
-      <c r="E128" s="15"/>
-      <c r="F128" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="G128" s="15" t="s">
-        <v>374</v>
-      </c>
-      <c r="H128" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="I128" s="15"/>
-      <c r="J128" s="15"/>
-      <c r="K128" s="15" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B128" t="s">
+        <v>111</v>
+      </c>
+      <c r="C128" t="s">
+        <v>83</v>
+      </c>
+      <c r="D128" t="s">
+        <v>96</v>
+      </c>
+      <c r="F128" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129" s="5">
         <v>128</v>
       </c>
-      <c r="B129" s="15" t="s">
-        <v>415</v>
-      </c>
-      <c r="C129" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D129" s="15" t="s">
-        <v>417</v>
-      </c>
-      <c r="E129" s="15"/>
-      <c r="F129" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="G129" s="15" t="s">
-        <v>374</v>
-      </c>
-      <c r="H129" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="I129" s="15"/>
-      <c r="J129" s="15" t="s">
-        <v>411</v>
-      </c>
-      <c r="K129" s="15"/>
-    </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B129" t="s">
+        <v>112</v>
+      </c>
+      <c r="C129" t="s">
+        <v>83</v>
+      </c>
+      <c r="D129" t="s">
+        <v>98</v>
+      </c>
+      <c r="F129" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130" s="5">
         <v>129</v>
       </c>
-      <c r="B130" s="15" t="s">
-        <v>421</v>
-      </c>
-      <c r="C130" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D130" s="15" t="s">
-        <v>422</v>
-      </c>
-      <c r="E130" s="15"/>
-      <c r="F130" s="15" t="s">
-        <v>265</v>
-      </c>
-      <c r="G130" s="15"/>
-      <c r="H130" s="15"/>
-      <c r="I130" s="15"/>
-      <c r="J130" s="15" t="s">
-        <v>423</v>
-      </c>
-      <c r="K130" s="15"/>
-    </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B130" t="s">
+        <v>113</v>
+      </c>
+      <c r="C130" t="s">
+        <v>75</v>
+      </c>
+      <c r="F130" t="s">
+        <v>13</v>
+      </c>
+      <c r="J130" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131" s="5">
         <v>130</v>
       </c>
-      <c r="B131" s="15" t="s">
-        <v>106</v>
-      </c>
-      <c r="C131" s="15"/>
-      <c r="D131" s="15"/>
-      <c r="E131" s="15"/>
-      <c r="F131" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="G131" s="15"/>
-      <c r="H131" s="15"/>
-      <c r="I131" s="15"/>
-      <c r="J131" s="15"/>
-      <c r="K131" s="15"/>
-    </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B131" t="s">
+        <v>114</v>
+      </c>
+      <c r="C131" t="s">
+        <v>75</v>
+      </c>
+      <c r="D131" t="s">
+        <v>77</v>
+      </c>
+      <c r="F131" t="s">
+        <v>42</v>
+      </c>
+      <c r="G131" t="s">
+        <v>46</v>
+      </c>
+      <c r="H131" t="s">
+        <v>47</v>
+      </c>
+      <c r="J131">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132" s="5">
         <v>131</v>
       </c>
-      <c r="B132" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="C132" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D132" s="15" t="s">
-        <v>412</v>
-      </c>
-      <c r="E132" s="15"/>
-      <c r="F132" s="15" t="s">
-        <v>439</v>
-      </c>
-      <c r="G132" s="15"/>
-      <c r="H132" s="15"/>
-      <c r="I132" s="15"/>
-      <c r="J132" s="15"/>
-      <c r="K132" s="15"/>
-    </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B132" t="s">
+        <v>115</v>
+      </c>
+      <c r="F132" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A133" s="5">
         <v>132</v>
       </c>
-      <c r="B133" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="C133" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D133" s="15"/>
-      <c r="E133" s="15"/>
-      <c r="F133" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G133" s="15"/>
-      <c r="H133" s="15"/>
-      <c r="I133" s="15"/>
-      <c r="J133" s="15"/>
-      <c r="K133" s="15"/>
-    </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B133" t="s">
+        <v>116</v>
+      </c>
+      <c r="C133" t="s">
+        <v>75</v>
+      </c>
+      <c r="D133" t="s">
+        <v>77</v>
+      </c>
+      <c r="F133" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A134" s="5">
         <v>133</v>
       </c>
-      <c r="B134" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="C134" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D134" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="E134" s="15"/>
-      <c r="F134" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G134" s="15"/>
-      <c r="H134" s="15"/>
-      <c r="I134" s="15"/>
-      <c r="J134" s="15"/>
-      <c r="K134" s="15"/>
-    </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B134" t="s">
+        <v>118</v>
+      </c>
+      <c r="C134" t="s">
+        <v>75</v>
+      </c>
+      <c r="F134" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A135" s="5">
         <v>134</v>
       </c>
-      <c r="B135" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="C135" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D135" s="15"/>
-      <c r="E135" s="15"/>
-      <c r="F135" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G135" s="15"/>
-      <c r="H135" s="15"/>
-      <c r="I135" s="15"/>
-      <c r="J135" s="15"/>
-      <c r="K135" s="15"/>
-    </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B135" t="s">
+        <v>119</v>
+      </c>
+      <c r="C135" t="s">
+        <v>120</v>
+      </c>
+      <c r="D135" t="s">
+        <v>121</v>
+      </c>
+      <c r="F135" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A136" s="5">
         <v>135</v>
       </c>
-      <c r="B136" s="15" t="s">
-        <v>112</v>
-      </c>
-      <c r="C136" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D136" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E136" s="15"/>
-      <c r="F136" s="15" t="s">
-        <v>437</v>
-      </c>
-      <c r="G136" s="15"/>
-      <c r="H136" s="15"/>
-      <c r="I136" s="15"/>
-      <c r="J136" s="15"/>
-      <c r="K136" s="15"/>
-    </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B136" t="s">
+        <v>122</v>
+      </c>
+      <c r="C136" t="s">
+        <v>123</v>
+      </c>
+      <c r="F136" t="s">
+        <v>13</v>
+      </c>
+      <c r="J136" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A137" s="5">
         <v>136</v>
       </c>
-      <c r="B137" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="C137" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D137" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="E137" s="15"/>
-      <c r="F137" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G137" s="15"/>
-      <c r="H137" s="15"/>
-      <c r="I137" s="15"/>
-      <c r="J137" s="15"/>
-      <c r="K137" s="15"/>
-    </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B137" t="s">
+        <v>124</v>
+      </c>
+      <c r="C137" t="s">
+        <v>123</v>
+      </c>
+      <c r="D137" t="s">
+        <v>125</v>
+      </c>
+      <c r="F137" t="s">
+        <v>42</v>
+      </c>
+      <c r="G137" t="s">
+        <v>46</v>
+      </c>
+      <c r="H137" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138" s="5">
         <v>137</v>
       </c>
-      <c r="B138" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="C138" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D138" s="15"/>
-      <c r="E138" s="15"/>
-      <c r="F138" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G138" s="15"/>
-      <c r="H138" s="15"/>
-      <c r="I138" s="15"/>
-      <c r="J138" s="15"/>
-      <c r="K138" s="15"/>
-    </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B138" t="s">
+        <v>126</v>
+      </c>
+      <c r="C138" t="s">
+        <v>123</v>
+      </c>
+      <c r="D138" t="s">
+        <v>94</v>
+      </c>
+      <c r="F138" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A139" s="5">
         <v>138</v>
       </c>
-      <c r="B139" s="15" t="s">
-        <v>116</v>
-      </c>
-      <c r="C139" s="15"/>
-      <c r="D139" s="15"/>
-      <c r="E139" s="15"/>
-      <c r="F139" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="G139" s="15"/>
-      <c r="H139" s="15"/>
-      <c r="I139" s="15"/>
-      <c r="J139" s="15"/>
-      <c r="K139" s="15"/>
-    </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B139" t="s">
+        <v>127</v>
+      </c>
+      <c r="C139" t="s">
+        <v>75</v>
+      </c>
+      <c r="F139" t="s">
+        <v>13</v>
+      </c>
+      <c r="J139">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A140" s="5">
         <v>139</v>
       </c>
-      <c r="B140" s="15" t="s">
-        <v>117</v>
-      </c>
-      <c r="C140" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D140" s="15" t="s">
-        <v>416</v>
-      </c>
-      <c r="E140" s="15"/>
-      <c r="F140" s="15" t="s">
-        <v>118</v>
-      </c>
-      <c r="G140" s="15"/>
-      <c r="H140" s="15"/>
-      <c r="I140" s="15"/>
-      <c r="J140" s="15"/>
-      <c r="K140" s="15"/>
-    </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B140" t="s">
+        <v>128</v>
+      </c>
+      <c r="F140" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A141" s="5">
         <v>140</v>
       </c>
-      <c r="B141" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="C141" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D141" s="15"/>
-      <c r="E141" s="15"/>
-      <c r="F141" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G141" s="15"/>
-      <c r="H141" s="15"/>
-      <c r="I141" s="15"/>
-      <c r="J141" s="15"/>
-      <c r="K141" s="15"/>
-    </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B141" t="s">
+        <v>129</v>
+      </c>
+      <c r="C141" t="s">
+        <v>75</v>
+      </c>
+      <c r="D141" t="s">
+        <v>77</v>
+      </c>
+      <c r="F141" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A142" s="5">
         <v>141</v>
       </c>
-      <c r="B142" s="15" t="s">
-        <v>419</v>
-      </c>
-      <c r="C142" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D142" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="E142" s="15"/>
-      <c r="F142" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G142" s="15"/>
-      <c r="H142" s="15"/>
-      <c r="I142" s="15"/>
-      <c r="J142" s="15"/>
-      <c r="K142" s="15"/>
-    </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B142" t="s">
+        <v>131</v>
+      </c>
+      <c r="C142" t="s">
+        <v>83</v>
+      </c>
+      <c r="F142" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A143" s="5">
         <v>142</v>
       </c>
-      <c r="B143" s="15" t="s">
-        <v>120</v>
-      </c>
-      <c r="C143" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D143" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="E143" s="15"/>
-      <c r="F143" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G143" s="15"/>
-      <c r="H143" s="15"/>
-      <c r="I143" s="15"/>
-      <c r="J143" s="15"/>
-      <c r="K143" s="15"/>
-    </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B143" t="s">
+        <v>132</v>
+      </c>
+      <c r="C143" t="s">
+        <v>83</v>
+      </c>
+      <c r="D143" t="s">
+        <v>133</v>
+      </c>
+      <c r="F143" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A144" s="5">
         <v>143</v>
       </c>
-      <c r="B144" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="C144" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D144" s="15"/>
-      <c r="E144" s="15"/>
-      <c r="F144" s="15" t="s">
+      <c r="B144" t="s">
+        <v>134</v>
+      </c>
+      <c r="C144" t="s">
+        <v>123</v>
+      </c>
+      <c r="F144" t="s">
         <v>13</v>
       </c>
-      <c r="G144" s="15"/>
-      <c r="H144" s="15"/>
-      <c r="I144" s="15"/>
-      <c r="J144" s="15"/>
-      <c r="K144" s="15"/>
-    </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.35">
+    </row>
+    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A145" s="5">
         <v>144</v>
       </c>
-      <c r="B145" s="15" t="s">
+      <c r="B145" t="s">
+        <v>135</v>
+      </c>
+      <c r="C145" t="s">
         <v>123</v>
       </c>
-      <c r="C145" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D145" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="E145" s="15"/>
-      <c r="F145" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G145" s="15"/>
-      <c r="H145" s="15"/>
-      <c r="I145" s="15"/>
-      <c r="J145" s="15"/>
-      <c r="K145" s="15"/>
-    </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="D145" t="s">
+        <v>136</v>
+      </c>
+      <c r="F145" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A146" s="5">
         <v>145</v>
       </c>
-      <c r="B146" s="15" t="s">
-        <v>420</v>
-      </c>
-      <c r="C146" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D146" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="E146" s="15"/>
-      <c r="F146" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G146" s="15"/>
-      <c r="H146" s="15"/>
-      <c r="I146" s="15"/>
-      <c r="J146" s="15"/>
-      <c r="K146" s="15"/>
-    </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B146" t="s">
+        <v>137</v>
+      </c>
+      <c r="C146" t="s">
+        <v>123</v>
+      </c>
+      <c r="D146" t="s">
+        <v>138</v>
+      </c>
+      <c r="F146" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A147" s="5">
         <v>146</v>
       </c>
-      <c r="B147" s="15" t="s">
-        <v>126</v>
-      </c>
-      <c r="C147" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D147" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="E147" s="15"/>
-      <c r="F147" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G147" s="15"/>
-      <c r="H147" s="15"/>
-      <c r="I147" s="15"/>
-      <c r="J147" s="15"/>
-      <c r="K147" s="15"/>
-    </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B147" t="s">
+        <v>139</v>
+      </c>
+      <c r="C147" t="s">
+        <v>123</v>
+      </c>
+      <c r="D147" t="s">
+        <v>94</v>
+      </c>
+      <c r="F147" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A148" s="5">
         <v>147</v>
       </c>
-      <c r="B148" s="15" t="s">
-        <v>127</v>
-      </c>
-      <c r="C148" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D148" s="15"/>
-      <c r="E148" s="15"/>
-      <c r="F148" s="15" t="s">
+      <c r="B148" t="s">
+        <v>140</v>
+      </c>
+      <c r="C148" t="s">
+        <v>83</v>
+      </c>
+      <c r="F148" t="s">
         <v>13</v>
       </c>
-      <c r="G148" s="15"/>
-      <c r="H148" s="15"/>
-      <c r="I148" s="15"/>
-      <c r="J148" s="15"/>
-      <c r="K148" s="15"/>
-    </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.35">
+    </row>
+    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A149" s="5">
         <v>148</v>
       </c>
-      <c r="B149" s="15" t="s">
-        <v>128</v>
-      </c>
-      <c r="C149" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D149" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="E149" s="15"/>
-      <c r="F149" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G149" s="15"/>
-      <c r="H149" s="15"/>
-      <c r="I149" s="15"/>
-      <c r="J149" s="15"/>
-      <c r="K149" s="15"/>
-    </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B149" t="s">
+        <v>141</v>
+      </c>
+      <c r="C149" t="s">
+        <v>83</v>
+      </c>
+      <c r="D149" t="s">
+        <v>98</v>
+      </c>
+      <c r="F149" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A150" s="5">
         <v>149</v>
       </c>
-      <c r="B150" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="C150" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D150" s="15"/>
-      <c r="E150" s="15"/>
-      <c r="F150" s="15" t="s">
+      <c r="B150" t="s">
+        <v>142</v>
+      </c>
+      <c r="C150" t="s">
+        <v>75</v>
+      </c>
+      <c r="F150" t="s">
         <v>13</v>
       </c>
-      <c r="G150" s="15"/>
-      <c r="H150" s="15"/>
-      <c r="I150" s="15"/>
-      <c r="J150" s="15"/>
-      <c r="K150" s="15"/>
-    </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="J150" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A151" s="5">
         <v>150</v>
       </c>
-      <c r="B151" s="15" t="s">
-        <v>424</v>
-      </c>
-      <c r="C151" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D151" s="15" t="s">
-        <v>422</v>
-      </c>
-      <c r="E151" s="15"/>
-      <c r="F151" s="15" t="s">
+      <c r="B151" t="s">
+        <v>143</v>
+      </c>
+      <c r="C151" t="s">
+        <v>75</v>
+      </c>
+      <c r="D151" t="s">
+        <v>77</v>
+      </c>
+      <c r="F151" t="s">
         <v>42</v>
       </c>
-      <c r="G151" s="15" t="s">
-        <v>374</v>
-      </c>
-      <c r="H151" s="15" t="s">
-        <v>425</v>
-      </c>
-      <c r="I151" s="15"/>
-      <c r="J151" s="15" t="s">
-        <v>423</v>
-      </c>
-      <c r="K151" s="15"/>
-    </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="G151" t="s">
+        <v>46</v>
+      </c>
+      <c r="H151" t="s">
+        <v>47</v>
+      </c>
+      <c r="J151">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A152" s="5">
         <v>151</v>
       </c>
-      <c r="B152" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="C152" s="15"/>
-      <c r="D152" s="15"/>
-      <c r="E152" s="15"/>
-      <c r="F152" s="15" t="s">
+      <c r="B152" t="s">
+        <v>144</v>
+      </c>
+      <c r="F152" t="s">
         <v>14</v>
       </c>
-      <c r="G152" s="15"/>
-      <c r="H152" s="15"/>
-      <c r="I152" s="15"/>
-      <c r="J152" s="15"/>
-      <c r="K152" s="15"/>
-    </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.35">
+    </row>
+    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A153" s="5">
         <v>152</v>
       </c>
-      <c r="B153" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="C153" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D153" s="15" t="s">
-        <v>416</v>
-      </c>
-      <c r="E153" s="15"/>
-      <c r="F153" s="15" t="s">
-        <v>418</v>
-      </c>
-      <c r="G153" s="15"/>
-      <c r="H153" s="15"/>
-      <c r="I153" s="15"/>
-      <c r="J153" s="15"/>
-      <c r="K153" s="15"/>
-    </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B153" t="s">
+        <v>145</v>
+      </c>
+      <c r="C153" t="s">
+        <v>75</v>
+      </c>
+      <c r="D153" t="s">
+        <v>77</v>
+      </c>
+      <c r="F153" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A154" s="5">
         <v>153</v>
       </c>
-      <c r="B154" s="15" t="s">
-        <v>132</v>
-      </c>
-      <c r="C154" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D154" s="15"/>
-      <c r="E154" s="15"/>
-      <c r="F154" s="15" t="s">
+      <c r="B154" t="s">
+        <v>146</v>
+      </c>
+      <c r="C154" t="s">
+        <v>83</v>
+      </c>
+      <c r="F154" t="s">
         <v>13</v>
       </c>
-      <c r="G154" s="15"/>
-      <c r="H154" s="15"/>
-      <c r="I154" s="15"/>
-      <c r="J154" s="15"/>
-      <c r="K154" s="15"/>
-    </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.35">
+    </row>
+    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A155" s="5">
         <v>154</v>
       </c>
-      <c r="B155" s="15" t="s">
-        <v>133</v>
-      </c>
-      <c r="C155" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D155" s="15" t="s">
-        <v>134</v>
-      </c>
-      <c r="E155" s="15"/>
-      <c r="F155" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G155" s="15"/>
-      <c r="H155" s="15"/>
-      <c r="I155" s="15"/>
-      <c r="J155" s="15"/>
-      <c r="K155" s="15"/>
-    </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B155" t="s">
+        <v>147</v>
+      </c>
+      <c r="C155" t="s">
+        <v>83</v>
+      </c>
+      <c r="D155" t="s">
+        <v>148</v>
+      </c>
+      <c r="F155" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A156" s="5">
         <v>155</v>
       </c>
-      <c r="B156" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="C156" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D156" s="15"/>
-      <c r="E156" s="15"/>
-      <c r="F156" s="15" t="s">
+      <c r="B156" t="s">
+        <v>149</v>
+      </c>
+      <c r="C156" t="s">
+        <v>83</v>
+      </c>
+      <c r="F156" t="s">
         <v>13</v>
       </c>
-      <c r="G156" s="15"/>
-      <c r="H156" s="15"/>
-      <c r="I156" s="15"/>
-      <c r="J156" s="15"/>
-    </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="K156" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A157" s="5">
         <v>156</v>
       </c>
-      <c r="B157" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="C157" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D157" s="15" t="s">
-        <v>137</v>
-      </c>
-      <c r="E157" s="15"/>
-      <c r="F157" s="15" t="s">
+      <c r="B157" t="s">
+        <v>150</v>
+      </c>
+      <c r="C157" t="s">
+        <v>83</v>
+      </c>
+      <c r="D157" t="s">
+        <v>151</v>
+      </c>
+      <c r="F157" t="s">
         <v>28</v>
       </c>
-      <c r="G157" s="15"/>
-      <c r="H157" s="15"/>
-      <c r="I157" s="15"/>
-      <c r="J157" s="15"/>
-      <c r="K157" s="15" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="K157" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="158" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A158" s="5">
         <v>157</v>
       </c>
-      <c r="B158" s="15" t="s">
-        <v>139</v>
-      </c>
-      <c r="C158" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D158" s="15" t="s">
-        <v>140</v>
-      </c>
-      <c r="E158" s="15"/>
-      <c r="F158" s="15" t="s">
+      <c r="B158" t="s">
+        <v>153</v>
+      </c>
+      <c r="C158" t="s">
+        <v>83</v>
+      </c>
+      <c r="D158" t="s">
+        <v>154</v>
+      </c>
+      <c r="F158" t="s">
         <v>28</v>
       </c>
-      <c r="G158" s="15"/>
-      <c r="H158" s="15"/>
-      <c r="I158" s="15"/>
-      <c r="J158" s="15"/>
-      <c r="K158" s="15" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.35">
+    </row>
+    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A159" s="5">
         <v>158</v>
       </c>
-      <c r="B159" s="15" t="s">
-        <v>142</v>
-      </c>
-      <c r="C159" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D159" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="E159" s="15"/>
-      <c r="F159" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G159" s="15"/>
-      <c r="H159" s="15"/>
-      <c r="I159" s="15"/>
-      <c r="J159" s="15"/>
-      <c r="K159" s="15"/>
-    </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B159" t="s">
+        <v>156</v>
+      </c>
+      <c r="C159" t="s">
+        <v>83</v>
+      </c>
+      <c r="D159" t="s">
+        <v>98</v>
+      </c>
+      <c r="F159" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A160" s="5">
         <v>159</v>
       </c>
-      <c r="B160" s="15" t="s">
-        <v>143</v>
-      </c>
-      <c r="C160" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D160" s="15"/>
-      <c r="E160" s="15"/>
-      <c r="F160" s="15" t="s">
+      <c r="B160" t="s">
+        <v>157</v>
+      </c>
+      <c r="C160" t="s">
+        <v>75</v>
+      </c>
+      <c r="F160" t="s">
         <v>13</v>
       </c>
-      <c r="G160" s="15"/>
-      <c r="H160" s="15"/>
-      <c r="I160" s="15"/>
-      <c r="J160" s="15"/>
-      <c r="K160" s="15"/>
-    </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.35">
+    </row>
+    <row r="161" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A161" s="5">
         <v>160</v>
       </c>
-      <c r="B161" s="15" t="s">
-        <v>144</v>
-      </c>
-      <c r="C161" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D161" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="E161" s="15"/>
-      <c r="F161" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G161" s="15"/>
-      <c r="H161" s="15"/>
-      <c r="I161" s="15"/>
-      <c r="J161" s="15"/>
-      <c r="K161" s="15"/>
-    </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B161" t="s">
+        <v>158</v>
+      </c>
+      <c r="C161" t="s">
+        <v>75</v>
+      </c>
+      <c r="D161" t="s">
+        <v>159</v>
+      </c>
+      <c r="F161" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="162" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A162" s="5">
         <v>161</v>
       </c>
-      <c r="B162" s="15" t="s">
-        <v>146</v>
-      </c>
-      <c r="C162" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D162" s="15"/>
-      <c r="E162" s="15"/>
-      <c r="F162" s="15" t="s">
+      <c r="B162" t="s">
+        <v>160</v>
+      </c>
+      <c r="C162" t="s">
+        <v>75</v>
+      </c>
+      <c r="F162" t="s">
         <v>13</v>
       </c>
-      <c r="G162" s="15"/>
-      <c r="H162" s="15"/>
-      <c r="I162" s="15"/>
-      <c r="J162" s="15" t="b">
+      <c r="J162" t="b">
         <v>1</v>
       </c>
-      <c r="K162" s="15"/>
-    </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.35">
+    </row>
+    <row r="163" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A163" s="5">
         <v>162</v>
       </c>
-      <c r="B163" s="15" t="s">
-        <v>414</v>
-      </c>
-      <c r="C163" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D163" s="15" t="s">
-        <v>416</v>
-      </c>
-      <c r="E163" s="15"/>
-      <c r="F163" s="15" t="s">
+      <c r="B163" t="s">
+        <v>161</v>
+      </c>
+      <c r="C163" t="s">
+        <v>75</v>
+      </c>
+      <c r="D163" t="s">
+        <v>159</v>
+      </c>
+      <c r="F163" t="s">
         <v>42</v>
       </c>
-      <c r="G163" s="15" t="s">
-        <v>374</v>
-      </c>
-      <c r="H163" s="15" t="s">
+      <c r="G163" t="s">
         <v>46</v>
       </c>
-      <c r="I163" s="15"/>
-      <c r="J163" s="15"/>
-      <c r="K163" s="15" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="H163" t="s">
+        <v>47</v>
+      </c>
+      <c r="J163">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A164" s="5">
         <v>163</v>
       </c>
-      <c r="B164" s="15" t="s">
-        <v>415</v>
-      </c>
-      <c r="C164" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D164" s="15" t="s">
-        <v>417</v>
-      </c>
-      <c r="E164" s="15"/>
-      <c r="F164" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="G164" s="15" t="s">
-        <v>374</v>
-      </c>
-      <c r="H164" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="I164" s="15"/>
-      <c r="J164" s="15" t="s">
-        <v>183</v>
-      </c>
-      <c r="K164" s="15"/>
-    </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B164" t="s">
+        <v>162</v>
+      </c>
+      <c r="F164" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="165" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A165" s="5">
         <v>164</v>
       </c>
-      <c r="B165" s="15" t="s">
-        <v>147</v>
-      </c>
-      <c r="C165" s="15"/>
-      <c r="D165" s="15"/>
-      <c r="E165" s="15"/>
-      <c r="F165" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="G165" s="15"/>
-      <c r="H165" s="15"/>
-      <c r="I165" s="15"/>
-      <c r="J165" s="15"/>
-      <c r="K165" s="15"/>
-    </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B165" t="s">
+        <v>163</v>
+      </c>
+      <c r="C165" t="s">
+        <v>75</v>
+      </c>
+      <c r="D165" t="s">
+        <v>77</v>
+      </c>
+      <c r="F165" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="166" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A166" s="5">
         <v>165</v>
       </c>
-      <c r="B166" s="15" t="s">
-        <v>428</v>
-      </c>
-      <c r="C166" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D166" s="15" t="s">
-        <v>412</v>
-      </c>
-      <c r="E166" s="15"/>
-      <c r="F166" s="15" t="s">
-        <v>439</v>
-      </c>
-      <c r="G166" s="15"/>
-      <c r="H166" s="15"/>
-      <c r="I166" s="15"/>
-      <c r="J166" s="15"/>
-      <c r="K166" s="15"/>
-    </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B166" t="s">
+        <v>118</v>
+      </c>
+      <c r="C166" t="s">
+        <v>75</v>
+      </c>
+      <c r="F166" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="167" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A167" s="5">
         <v>166</v>
       </c>
-      <c r="B167" s="15" t="s">
-        <v>108</v>
-      </c>
-      <c r="C167" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D167" s="15"/>
-      <c r="E167" s="15"/>
-      <c r="F167" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G167" s="15"/>
-      <c r="H167" s="15"/>
-      <c r="I167" s="15"/>
-      <c r="J167" s="15"/>
-      <c r="K167" s="15"/>
-    </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B167" t="s">
+        <v>164</v>
+      </c>
+      <c r="C167" t="s">
+        <v>120</v>
+      </c>
+      <c r="D167" t="s">
+        <v>165</v>
+      </c>
+      <c r="F167" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="168" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A168" s="5">
         <v>167</v>
       </c>
-      <c r="B168" s="15" t="s">
-        <v>148</v>
-      </c>
-      <c r="C168" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D168" s="15" t="s">
-        <v>149</v>
-      </c>
-      <c r="E168" s="15"/>
-      <c r="F168" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G168" s="15"/>
-      <c r="H168" s="15"/>
-      <c r="I168" s="15"/>
-      <c r="J168" s="15"/>
-      <c r="K168" s="15"/>
-    </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B168" t="s">
+        <v>166</v>
+      </c>
+      <c r="C168" t="s">
+        <v>167</v>
+      </c>
+      <c r="F168" t="s">
+        <v>13</v>
+      </c>
+      <c r="K168" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="169" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A169" s="5">
         <v>168</v>
       </c>
-      <c r="B169" s="15" t="s">
-        <v>150</v>
-      </c>
-      <c r="C169" s="15" t="s">
-        <v>427</v>
-      </c>
-      <c r="D169" s="15"/>
-      <c r="E169" s="15"/>
-      <c r="F169" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G169" s="15"/>
-      <c r="H169" s="15"/>
-      <c r="I169" s="15"/>
-      <c r="J169" s="15"/>
-      <c r="K169" s="15"/>
-    </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B169" t="s">
+        <v>168</v>
+      </c>
+      <c r="C169" t="s">
+        <v>167</v>
+      </c>
+      <c r="D169" t="s">
+        <v>169</v>
+      </c>
+      <c r="F169" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="170" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A170" s="5">
         <v>169</v>
       </c>
-      <c r="B170" s="15" t="s">
-        <v>151</v>
-      </c>
-      <c r="C170" s="15" t="s">
-        <v>427</v>
-      </c>
-      <c r="D170" s="15" t="s">
-        <v>152</v>
-      </c>
-      <c r="E170" s="15"/>
-      <c r="F170" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="G170" s="15"/>
-      <c r="H170" s="15"/>
-      <c r="I170" s="15"/>
-      <c r="J170" s="15"/>
-      <c r="K170" s="15" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B170" t="s">
+        <v>171</v>
+      </c>
+      <c r="C170" t="s">
+        <v>167</v>
+      </c>
+      <c r="D170" t="s">
+        <v>65</v>
+      </c>
+      <c r="F170" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="171" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A171" s="5">
         <v>170</v>
       </c>
-      <c r="B171" s="15" t="s">
-        <v>154</v>
-      </c>
-      <c r="C171" s="15" t="s">
-        <v>427</v>
-      </c>
-      <c r="D171" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="E171" s="15"/>
-      <c r="F171" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G171" s="15"/>
-      <c r="H171" s="15"/>
-      <c r="I171" s="15"/>
-      <c r="J171" s="15"/>
-      <c r="K171" s="15"/>
-    </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B171" t="s">
+        <v>172</v>
+      </c>
+      <c r="C171" t="s">
+        <v>167</v>
+      </c>
+      <c r="F171" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="172" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A172" s="5">
         <v>171</v>
       </c>
-      <c r="B172" s="15" t="s">
-        <v>155</v>
-      </c>
-      <c r="C172" s="15" t="s">
-        <v>427</v>
-      </c>
-      <c r="D172" s="15"/>
-      <c r="E172" s="15"/>
-      <c r="F172" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G172" s="15"/>
-      <c r="H172" s="15"/>
-      <c r="I172" s="15"/>
-      <c r="J172" s="15"/>
-      <c r="K172" s="15"/>
-    </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B172" t="s">
+        <v>173</v>
+      </c>
+      <c r="C172" t="s">
+        <v>167</v>
+      </c>
+      <c r="D172" t="s">
+        <v>40</v>
+      </c>
+      <c r="F172" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="173" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A173" s="5">
         <v>172</v>
       </c>
-      <c r="B173" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="C173" s="15" t="s">
-        <v>427</v>
-      </c>
-      <c r="D173" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="E173" s="15"/>
-      <c r="F173" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G173" s="15"/>
-      <c r="H173" s="15"/>
-      <c r="I173" s="15"/>
-      <c r="J173" s="15"/>
-      <c r="K173" s="15"/>
-    </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B173" t="s">
+        <v>174</v>
+      </c>
+      <c r="C173" t="s">
+        <v>75</v>
+      </c>
+      <c r="F173" t="s">
+        <v>13</v>
+      </c>
+      <c r="J173" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A174" s="5">
         <v>173</v>
       </c>
-      <c r="B174" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="C174" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D174" s="15"/>
-      <c r="E174" s="15"/>
-      <c r="F174" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G174" s="15"/>
-      <c r="H174" s="15"/>
-      <c r="I174" s="15"/>
-      <c r="J174" s="15"/>
-      <c r="K174" s="15"/>
-    </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B174" t="s">
+        <v>175</v>
+      </c>
+      <c r="C174" t="s">
+        <v>75</v>
+      </c>
+      <c r="D174" t="s">
+        <v>77</v>
+      </c>
+      <c r="F174" t="s">
+        <v>42</v>
+      </c>
+      <c r="G174" t="s">
+        <v>46</v>
+      </c>
+      <c r="H174" t="s">
+        <v>47</v>
+      </c>
+      <c r="J174">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="175" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A175" s="5">
         <v>174</v>
       </c>
-      <c r="B175" s="15" t="s">
-        <v>429</v>
-      </c>
-      <c r="C175" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D175" s="15" t="s">
-        <v>430</v>
-      </c>
-      <c r="E175" s="15"/>
-      <c r="F175" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G175" s="15"/>
-      <c r="H175" s="15"/>
-      <c r="I175" s="15"/>
-      <c r="J175" s="15"/>
-      <c r="K175" s="15"/>
-    </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B175" t="s">
+        <v>176</v>
+      </c>
+      <c r="F175" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="176" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A176" s="5">
         <v>175</v>
       </c>
-      <c r="B176" s="15" t="s">
-        <v>158</v>
-      </c>
-      <c r="C176" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D176" s="15" t="s">
-        <v>431</v>
-      </c>
-      <c r="E176" s="15"/>
-      <c r="F176" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="G176" s="15" t="s">
-        <v>374</v>
-      </c>
-      <c r="H176" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="I176" s="15"/>
-      <c r="J176" s="15"/>
-      <c r="K176" s="15" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B176" t="s">
+        <v>177</v>
+      </c>
+      <c r="C176" t="s">
+        <v>75</v>
+      </c>
+      <c r="D176" t="s">
+        <v>77</v>
+      </c>
+      <c r="F176" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="177" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A177" s="5">
         <v>176</v>
       </c>
-      <c r="B177" s="15" t="s">
-        <v>159</v>
-      </c>
-      <c r="C177" s="15"/>
-      <c r="D177" s="15"/>
-      <c r="E177" s="15"/>
-      <c r="F177" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="G177" s="15"/>
-      <c r="H177" s="15"/>
-      <c r="I177" s="15"/>
-      <c r="J177" s="15"/>
-      <c r="K177" s="15"/>
-    </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B177" t="s">
+        <v>178</v>
+      </c>
+      <c r="C177" t="s">
+        <v>83</v>
+      </c>
+      <c r="F177" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="178" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A178" s="5">
         <v>177</v>
       </c>
-      <c r="B178" s="15" t="s">
-        <v>132</v>
-      </c>
-      <c r="C178" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D178" s="15"/>
-      <c r="E178" s="15"/>
-      <c r="F178" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G178" s="15"/>
-      <c r="H178" s="15"/>
-      <c r="I178" s="15"/>
-      <c r="J178" s="15"/>
-      <c r="K178" s="15"/>
-    </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B178" t="s">
+        <v>179</v>
+      </c>
+      <c r="C178" t="s">
+        <v>83</v>
+      </c>
+      <c r="D178" t="s">
+        <v>148</v>
+      </c>
+      <c r="F178" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="179" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A179" s="5">
         <v>178</v>
       </c>
-      <c r="B179" s="15" t="s">
-        <v>433</v>
-      </c>
-      <c r="C179" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D179" s="15" t="s">
-        <v>416</v>
-      </c>
-      <c r="E179" s="15"/>
-      <c r="F179" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G179" s="15"/>
-      <c r="H179" s="15"/>
-      <c r="I179" s="15"/>
-      <c r="J179" s="15"/>
-      <c r="K179" s="15"/>
-    </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B179" t="s">
+        <v>149</v>
+      </c>
+      <c r="C179" t="s">
+        <v>83</v>
+      </c>
+      <c r="F179" t="s">
+        <v>13</v>
+      </c>
+      <c r="K179" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="180" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A180" s="5">
         <v>179</v>
       </c>
-      <c r="B180" s="15" t="s">
-        <v>434</v>
-      </c>
-      <c r="C180" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D180" s="15"/>
-      <c r="E180" s="15"/>
-      <c r="F180" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G180" s="15"/>
-      <c r="H180" s="15"/>
-      <c r="I180" s="15"/>
-      <c r="J180" s="15"/>
-      <c r="K180" s="15"/>
-    </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B180" t="s">
+        <v>180</v>
+      </c>
+      <c r="C180" t="s">
+        <v>83</v>
+      </c>
+      <c r="D180" t="s">
+        <v>151</v>
+      </c>
+      <c r="F180" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="181" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A181" s="5">
         <v>180</v>
       </c>
-      <c r="B181" s="15" t="s">
-        <v>160</v>
-      </c>
-      <c r="C181" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D181" s="15" t="s">
-        <v>134</v>
-      </c>
-      <c r="E181" s="15"/>
-      <c r="F181" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G181" s="15"/>
-      <c r="H181" s="15"/>
-      <c r="I181" s="15"/>
-      <c r="J181" s="15"/>
-      <c r="K181" s="15"/>
-    </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B181" t="s">
+        <v>182</v>
+      </c>
+      <c r="C181" t="s">
+        <v>83</v>
+      </c>
+      <c r="D181" t="s">
+        <v>98</v>
+      </c>
+      <c r="F181" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="182" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A182" s="5">
         <v>181</v>
       </c>
-      <c r="B182" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="C182" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D182" s="15"/>
-      <c r="E182" s="15"/>
-      <c r="F182" s="15" t="s">
+      <c r="B182" t="s">
+        <v>183</v>
+      </c>
+      <c r="C182" t="s">
+        <v>75</v>
+      </c>
+      <c r="F182" t="s">
         <v>13</v>
       </c>
-      <c r="G182" s="15"/>
-      <c r="H182" s="15"/>
-      <c r="I182" s="15"/>
-      <c r="J182" s="15"/>
-      <c r="K182" s="15"/>
-    </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.35">
+    </row>
+    <row r="183" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A183" s="5">
         <v>182</v>
       </c>
-      <c r="B183" s="15" t="s">
-        <v>161</v>
-      </c>
-      <c r="C183" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D183" s="15" t="s">
-        <v>137</v>
-      </c>
-      <c r="E183" s="15"/>
-      <c r="F183" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="G183" s="15"/>
-      <c r="H183" s="15"/>
-      <c r="I183" s="15"/>
-      <c r="J183" s="15"/>
-      <c r="K183" s="15" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B183" t="s">
+        <v>184</v>
+      </c>
+      <c r="C183" t="s">
+        <v>75</v>
+      </c>
+      <c r="D183" t="s">
+        <v>159</v>
+      </c>
+      <c r="F183" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="184" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A184" s="5">
         <v>183</v>
       </c>
-      <c r="B184" s="15" t="s">
-        <v>163</v>
-      </c>
-      <c r="C184" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D184" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="E184" s="15"/>
-      <c r="F184" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G184" s="15"/>
-      <c r="H184" s="15"/>
-      <c r="I184" s="15"/>
-      <c r="J184" s="15"/>
-      <c r="K184" s="15"/>
-    </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B184" t="s">
+        <v>185</v>
+      </c>
+      <c r="C184" t="s">
+        <v>75</v>
+      </c>
+      <c r="F184" t="s">
+        <v>13</v>
+      </c>
+      <c r="J184" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A185" s="5">
         <v>184</v>
       </c>
-      <c r="B185" s="15" t="s">
-        <v>164</v>
-      </c>
-      <c r="C185" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D185" s="15"/>
-      <c r="E185" s="15"/>
-      <c r="F185" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G185" s="15"/>
-      <c r="H185" s="15"/>
-      <c r="I185" s="15"/>
-      <c r="J185" s="15"/>
-      <c r="K185" s="15"/>
-    </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B185" t="s">
+        <v>186</v>
+      </c>
+      <c r="C185" t="s">
+        <v>75</v>
+      </c>
+      <c r="D185" t="s">
+        <v>159</v>
+      </c>
+      <c r="F185" t="s">
+        <v>42</v>
+      </c>
+      <c r="G185" t="s">
+        <v>46</v>
+      </c>
+      <c r="H185" t="s">
+        <v>47</v>
+      </c>
+      <c r="J185">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="186" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A186" s="5">
         <v>185</v>
       </c>
-      <c r="B186" s="15" t="s">
-        <v>165</v>
-      </c>
-      <c r="C186" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="D186" s="15" t="s">
-        <v>438</v>
-      </c>
-      <c r="E186" s="15"/>
-      <c r="F186" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G186" s="15"/>
-      <c r="H186" s="15"/>
-      <c r="I186" s="15"/>
-      <c r="J186" s="15"/>
-      <c r="K186" s="15"/>
-    </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B186" t="s">
+        <v>187</v>
+      </c>
+      <c r="F186" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="187" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A187" s="5">
         <v>186</v>
       </c>
-      <c r="B187" s="15" t="s">
-        <v>166</v>
-      </c>
-      <c r="C187" s="5" t="s">
+      <c r="B187" t="s">
+        <v>188</v>
+      </c>
+      <c r="C187" t="s">
         <v>12</v>
       </c>
-      <c r="D187" s="15"/>
-      <c r="E187" s="15"/>
-      <c r="F187" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="G187" s="15"/>
-      <c r="H187" s="15"/>
-      <c r="I187" s="15"/>
-      <c r="J187" s="15"/>
-      <c r="K187" s="15"/>
-    </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="D187" t="s">
+        <v>189</v>
+      </c>
+      <c r="F187" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="188" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A188" s="5">
         <v>187</v>
       </c>
-      <c r="B188" s="15" t="s">
-        <v>435</v>
-      </c>
-      <c r="C188" s="5" t="s">
+      <c r="B188" t="s">
+        <v>190</v>
+      </c>
+      <c r="C188" t="s">
         <v>12</v>
       </c>
-      <c r="D188" s="15" t="s">
-        <v>417</v>
-      </c>
-      <c r="E188" s="15"/>
-      <c r="F188" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="G188" s="15" t="s">
-        <v>374</v>
-      </c>
-      <c r="H188" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="I188" s="15"/>
-      <c r="J188" s="15" t="s">
-        <v>432</v>
-      </c>
-      <c r="K188" s="15"/>
-    </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="D188" t="s">
+        <v>191</v>
+      </c>
+      <c r="F188" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="189" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A189" s="5">
         <v>188</v>
       </c>
-      <c r="B189" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="C189" s="15"/>
-      <c r="D189" s="15"/>
-      <c r="E189" s="15"/>
-      <c r="F189" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="G189" s="15"/>
-      <c r="H189" s="15"/>
-      <c r="I189" s="15"/>
-      <c r="J189" s="15"/>
-      <c r="K189" s="15"/>
-    </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A190" s="5">
-        <v>189</v>
-      </c>
-      <c r="B190" s="15" t="s">
-        <v>168</v>
-      </c>
-      <c r="C190" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="D190" s="15" t="s">
-        <v>169</v>
-      </c>
-      <c r="E190" s="15"/>
-      <c r="F190" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G190" s="15"/>
-      <c r="H190" s="15"/>
-      <c r="I190" s="15"/>
-      <c r="J190" s="15"/>
-      <c r="K190" s="15"/>
-    </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A191" s="5">
-        <v>190</v>
-      </c>
-      <c r="B191" s="15" t="s">
-        <v>170</v>
-      </c>
-      <c r="C191" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="D191" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="E191" s="15"/>
-      <c r="F191" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="G191" s="15"/>
-      <c r="H191" s="15"/>
-      <c r="I191" s="15"/>
-      <c r="J191" s="15"/>
-      <c r="K191" s="15"/>
+      <c r="B189" t="s">
+        <v>192</v>
+      </c>
+      <c r="C189" t="s">
+        <v>11</v>
+      </c>
+      <c r="F189" t="s">
+        <v>13</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="4">
@@ -6495,34 +5746,34 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C258D142-3A59-487D-A059-DA6AFF2F4605}">
   <dimension ref="A1:AE2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.08984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="19" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.36328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.90625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.08984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20.54296875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20.5703125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="21" bestFit="1" customWidth="1"/>
     <col min="14" max="22" width="21" customWidth="1"/>
-    <col min="23" max="23" width="21.453125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="16.140625" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="17" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="16.140625" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="17" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="17.36328125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="18.08984375" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="25.6328125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="18.90625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="18.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>25</v>
       </c>
@@ -6562,70 +5813,70 @@
       <c r="M1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="N1" s="14" t="s">
-        <v>303</v>
-      </c>
-      <c r="O1" s="14" t="s">
-        <v>306</v>
-      </c>
-      <c r="P1" s="14" t="s">
-        <v>321</v>
-      </c>
-      <c r="Q1" s="14" t="s">
-        <v>327</v>
-      </c>
-      <c r="R1" s="14" t="s">
-        <v>330</v>
-      </c>
-      <c r="S1" s="14" t="s">
-        <v>333</v>
-      </c>
-      <c r="T1" s="14" t="s">
-        <v>336</v>
-      </c>
-      <c r="U1" s="14" t="s">
-        <v>382</v>
-      </c>
-      <c r="V1" s="14" t="s">
-        <v>383</v>
+      <c r="N1" s="15" t="s">
+        <v>326</v>
+      </c>
+      <c r="O1" s="15" t="s">
+        <v>329</v>
+      </c>
+      <c r="P1" s="15" t="s">
+        <v>344</v>
+      </c>
+      <c r="Q1" s="15" t="s">
+        <v>350</v>
+      </c>
+      <c r="R1" s="15" t="s">
+        <v>353</v>
+      </c>
+      <c r="S1" s="15" t="s">
+        <v>356</v>
+      </c>
+      <c r="T1" s="15" t="s">
+        <v>359</v>
+      </c>
+      <c r="U1" s="15" t="s">
+        <v>405</v>
+      </c>
+      <c r="V1" s="15" t="s">
+        <v>406</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="C2" t="s">
-        <v>258</v>
+        <v>281</v>
       </c>
       <c r="D2" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="E2">
         <v>1234567890</v>
@@ -6634,79 +5885,79 @@
         <v>7700900000</v>
       </c>
       <c r="G2" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="H2" t="s">
-        <v>175</v>
+        <v>196</v>
       </c>
       <c r="I2" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="J2" t="s">
-        <v>176</v>
+        <v>197</v>
       </c>
       <c r="K2" t="s">
-        <v>177</v>
+        <v>198</v>
       </c>
       <c r="L2" t="s">
-        <v>177</v>
+        <v>198</v>
       </c>
       <c r="M2" t="s">
-        <v>178</v>
+        <v>199</v>
       </c>
       <c r="N2" t="s">
-        <v>280</v>
+        <v>303</v>
       </c>
       <c r="O2">
         <v>3</v>
       </c>
       <c r="P2" t="s">
-        <v>384</v>
+        <v>407</v>
       </c>
       <c r="Q2" t="s">
-        <v>385</v>
+        <v>408</v>
       </c>
       <c r="R2" t="s">
-        <v>386</v>
+        <v>409</v>
       </c>
       <c r="S2" t="s">
-        <v>274</v>
+        <v>297</v>
       </c>
       <c r="T2" t="s">
-        <v>387</v>
+        <v>410</v>
       </c>
       <c r="U2" t="s">
-        <v>388</v>
+        <v>411</v>
       </c>
       <c r="V2" t="s">
-        <v>389</v>
+        <v>412</v>
       </c>
       <c r="W2" t="s">
-        <v>179</v>
+        <v>200</v>
       </c>
       <c r="X2" t="s">
-        <v>180</v>
+        <v>201</v>
       </c>
       <c r="Y2" t="s">
-        <v>181</v>
+        <v>202</v>
       </c>
       <c r="Z2" t="s">
-        <v>180</v>
+        <v>201</v>
       </c>
       <c r="AA2" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="AB2" t="s">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="AC2" t="s">
-        <v>426</v>
+        <v>205</v>
       </c>
       <c r="AD2" t="s">
-        <v>184</v>
+        <v>206</v>
       </c>
       <c r="AE2" t="s">
-        <v>432</v>
+        <v>207</v>
       </c>
     </row>
   </sheetData>
@@ -6717,170 +5968,170 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{228C5EE8-5242-4BA3-97AC-567590037670}">
   <dimension ref="A1:B20"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.6328125" customWidth="1"/>
-    <col min="2" max="2" width="94.453125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="27.7109375" customWidth="1"/>
+    <col min="2" max="2" width="94.42578125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>185</v>
+        <v>208</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>187</v>
+        <v>210</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>189</v>
+        <v>212</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>191</v>
+        <v>214</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>193</v>
+        <v>216</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>195</v>
+        <v>218</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>197</v>
+        <v>220</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>199</v>
+        <v>222</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>201</v>
+        <v>224</v>
       </c>
       <c r="B9" s="3">
         <v>153</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>202</v>
+        <v>225</v>
       </c>
       <c r="B10" s="3">
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>203</v>
+        <v>226</v>
       </c>
       <c r="B11" s="3">
         <v>55</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>204</v>
+        <v>227</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>206</v>
+        <v>229</v>
       </c>
       <c r="B13" s="4">
         <v>46147</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>207</v>
+        <v>230</v>
       </c>
       <c r="B14" s="4">
         <v>46147</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>208</v>
+        <v>231</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>210</v>
+        <v>233</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>212</v>
+        <v>235</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>214</v>
+        <v>237</v>
       </c>
       <c r="B18" s="3">
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>218</v>
+        <v>241</v>
       </c>
     </row>
   </sheetData>
@@ -6891,86 +6142,80 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46043604-D720-4D74-A326-50042A6D73F4}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="55.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="55.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>193</v>
+        <v>216</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="C2" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>41</v>
       </c>
       <c r="B3" t="s">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="C3" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="B4" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="C4" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>227</v>
+        <v>250</v>
       </c>
       <c r="B5" t="s">
-        <v>228</v>
+        <v>251</v>
       </c>
       <c r="C5" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>230</v>
+        <v>253</v>
       </c>
       <c r="B6" t="s">
-        <v>231</v>
+        <v>254</v>
       </c>
       <c r="C6" t="s">
-        <v>229</v>
+        <v>252</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
-<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{a4153a30-97aa-49dd-8839-66f72081522c}" enabled="1" method="Standard" siteId="{9ffff5c3-bdfa-4a9d-b595-ff68329945ef}" contentBits="0" removed="0"/>
-</clbl:labelList>
 </file>
--- a/lorenzo-playwright-kdf/excelFramework/testcases/Problems/LSTP_Problems_WF001.xlsx
+++ b/lorenzo-playwright-kdf/excelFramework/testcases/Problems/LSTP_Problems_WF001.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkrishnan6\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\Problems\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1CBC404-6F25-494F-9768-85AD290D9B97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0567B2BB-0B8B-45CE-811E-262DE8705FDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1335" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{BE3DF6D1-393A-4573-8176-869B7BDB99D6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{BE3DF6D1-393A-4573-8176-869B7BDB99D6}"/>
   </bookViews>
   <sheets>
     <sheet name="TestExecution" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="340">
   <si>
     <t>StepNo</t>
   </si>
@@ -78,9 +78,6 @@
   </si>
   <si>
     <t>launchUrl</t>
-  </si>
-  <si>
-    <t>http://dxcappchne8097a.cscidp.net/webclient_sso/extlogon.aspx?idp=oidnatlogon&amp;IsClientInfoNotRequired=true</t>
   </si>
   <si>
     <t>Login with valid credentials</t>
@@ -1518,25 +1515,22 @@
       <c r="F2" t="s">
         <v>12</v>
       </c>
-      <c r="J2" t="s">
-        <v>13</v>
-      </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" t="s">
+      <c r="F3" t="s">
         <v>15</v>
       </c>
-      <c r="F3" t="s">
+      <c r="J3" t="s">
         <v>16</v>
-      </c>
-      <c r="J3" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -1544,13 +1538,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
         <v>18</v>
       </c>
-      <c r="C4" t="s">
+      <c r="F4" t="s">
         <v>19</v>
-      </c>
-      <c r="F4" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -1558,10 +1552,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" t="s">
         <v>21</v>
-      </c>
-      <c r="F5" t="s">
-        <v>22</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -1572,16 +1566,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" t="s">
         <v>23</v>
       </c>
-      <c r="C6" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" t="s">
-        <v>24</v>
-      </c>
       <c r="F6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -1589,13 +1583,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" t="s">
         <v>19</v>
-      </c>
-      <c r="F7" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -1603,16 +1597,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" t="s">
         <v>27</v>
       </c>
-      <c r="C8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" t="s">
-        <v>28</v>
-      </c>
       <c r="F8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
@@ -1620,13 +1614,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" t="s">
         <v>19</v>
-      </c>
-      <c r="F9" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
@@ -1634,13 +1628,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
+        <v>29</v>
+      </c>
+      <c r="F10" t="s">
         <v>30</v>
       </c>
-      <c r="F10" t="s">
+      <c r="J10" t="s">
         <v>31</v>
-      </c>
-      <c r="J10" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
@@ -1648,19 +1642,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" t="s">
         <v>33</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>34</v>
       </c>
-      <c r="D11" t="s">
+      <c r="F11" t="s">
         <v>35</v>
       </c>
-      <c r="F11" t="s">
+      <c r="J11" t="s">
         <v>36</v>
-      </c>
-      <c r="J11" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
@@ -1668,16 +1662,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" t="s">
         <v>38</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>39</v>
       </c>
-      <c r="D12" t="s">
-        <v>40</v>
-      </c>
       <c r="F12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
@@ -1685,13 +1679,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C13" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1699,13 +1693,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
+        <v>41</v>
+      </c>
+      <c r="F14" t="s">
         <v>42</v>
       </c>
-      <c r="F14" t="s">
+      <c r="J14" t="s">
         <v>43</v>
-      </c>
-      <c r="J14" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -1713,13 +1707,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
+        <v>44</v>
+      </c>
+      <c r="C15" t="s">
         <v>45</v>
       </c>
-      <c r="C15" t="s">
-        <v>46</v>
-      </c>
       <c r="F15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -1727,19 +1721,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" t="s">
         <v>47</v>
       </c>
-      <c r="C16" t="s">
-        <v>46</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="F16" t="s">
+        <v>35</v>
+      </c>
+      <c r="K16" t="s">
         <v>48</v>
-      </c>
-      <c r="F16" t="s">
-        <v>36</v>
-      </c>
-      <c r="K16" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -1747,19 +1741,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D17" t="s">
+        <v>34</v>
+      </c>
+      <c r="F17" t="s">
         <v>35</v>
       </c>
-      <c r="F17" t="s">
+      <c r="J17" t="s">
         <v>36</v>
-      </c>
-      <c r="J17" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
@@ -1767,16 +1761,16 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
+        <v>50</v>
+      </c>
+      <c r="C18" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18" t="s">
         <v>51</v>
       </c>
-      <c r="C18" t="s">
-        <v>46</v>
-      </c>
-      <c r="D18" t="s">
-        <v>52</v>
-      </c>
       <c r="F18" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
@@ -1784,19 +1778,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" t="s">
+        <v>45</v>
+      </c>
+      <c r="D19" t="s">
         <v>53</v>
       </c>
-      <c r="C19" t="s">
-        <v>46</v>
-      </c>
-      <c r="D19" t="s">
+      <c r="F19" t="s">
+        <v>35</v>
+      </c>
+      <c r="K19" t="s">
         <v>54</v>
-      </c>
-      <c r="F19" t="s">
-        <v>36</v>
-      </c>
-      <c r="K19" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
@@ -1804,16 +1798,16 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C20" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F20" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
@@ -1821,13 +1815,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C21" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F21" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
@@ -1835,16 +1829,16 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
+        <v>57</v>
+      </c>
+      <c r="C22" t="s">
+        <v>45</v>
+      </c>
+      <c r="D22" t="s">
         <v>58</v>
       </c>
-      <c r="C22" t="s">
-        <v>46</v>
-      </c>
-      <c r="D22" t="s">
-        <v>59</v>
-      </c>
       <c r="F22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
@@ -1852,19 +1846,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
+        <v>59</v>
+      </c>
+      <c r="C23" t="s">
+        <v>45</v>
+      </c>
+      <c r="D23" t="s">
         <v>60</v>
       </c>
-      <c r="C23" t="s">
-        <v>46</v>
-      </c>
-      <c r="D23" t="s">
+      <c r="F23" t="s">
+        <v>35</v>
+      </c>
+      <c r="K23" t="s">
         <v>61</v>
-      </c>
-      <c r="F23" t="s">
-        <v>36</v>
-      </c>
-      <c r="K23" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
@@ -1872,19 +1866,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
+        <v>62</v>
+      </c>
+      <c r="C24" t="s">
+        <v>45</v>
+      </c>
+      <c r="D24" t="s">
         <v>63</v>
       </c>
-      <c r="C24" t="s">
-        <v>46</v>
-      </c>
-      <c r="D24" t="s">
+      <c r="F24" t="s">
         <v>64</v>
       </c>
-      <c r="F24" t="s">
+      <c r="K24" t="s">
         <v>65</v>
-      </c>
-      <c r="K24" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
@@ -1892,19 +1886,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
+        <v>66</v>
+      </c>
+      <c r="C25" t="s">
+        <v>45</v>
+      </c>
+      <c r="D25" t="s">
         <v>67</v>
       </c>
-      <c r="C25" t="s">
-        <v>46</v>
-      </c>
-      <c r="D25" t="s">
+      <c r="F25" t="s">
+        <v>35</v>
+      </c>
+      <c r="K25" t="s">
         <v>68</v>
-      </c>
-      <c r="F25" t="s">
-        <v>36</v>
-      </c>
-      <c r="K25" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -1912,19 +1906,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
+        <v>69</v>
+      </c>
+      <c r="C26" t="s">
+        <v>45</v>
+      </c>
+      <c r="D26" t="s">
         <v>70</v>
       </c>
-      <c r="C26" t="s">
-        <v>46</v>
-      </c>
-      <c r="D26" t="s">
+      <c r="F26" t="s">
+        <v>35</v>
+      </c>
+      <c r="K26" t="s">
         <v>71</v>
-      </c>
-      <c r="F26" t="s">
-        <v>36</v>
-      </c>
-      <c r="K26" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
@@ -1932,19 +1926,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
+        <v>72</v>
+      </c>
+      <c r="C27" t="s">
+        <v>45</v>
+      </c>
+      <c r="D27" t="s">
         <v>73</v>
       </c>
-      <c r="C27" t="s">
-        <v>46</v>
-      </c>
-      <c r="D27" t="s">
+      <c r="F27" t="s">
+        <v>35</v>
+      </c>
+      <c r="K27" t="s">
         <v>74</v>
-      </c>
-      <c r="F27" t="s">
-        <v>36</v>
-      </c>
-      <c r="K27" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -1952,16 +1946,16 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
+        <v>75</v>
+      </c>
+      <c r="C28" t="s">
+        <v>45</v>
+      </c>
+      <c r="D28" t="s">
         <v>76</v>
       </c>
-      <c r="C28" t="s">
-        <v>46</v>
-      </c>
-      <c r="D28" t="s">
-        <v>77</v>
-      </c>
       <c r="F28" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
@@ -1969,13 +1963,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C29" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F29" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
@@ -1983,19 +1977,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
+        <v>78</v>
+      </c>
+      <c r="C30" t="s">
+        <v>45</v>
+      </c>
+      <c r="D30" t="s">
         <v>79</v>
       </c>
-      <c r="C30" t="s">
-        <v>46</v>
-      </c>
-      <c r="D30" t="s">
+      <c r="F30" t="s">
+        <v>64</v>
+      </c>
+      <c r="K30" t="s">
         <v>80</v>
-      </c>
-      <c r="F30" t="s">
-        <v>65</v>
-      </c>
-      <c r="K30" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -2003,19 +1997,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
+        <v>81</v>
+      </c>
+      <c r="C31" t="s">
+        <v>45</v>
+      </c>
+      <c r="D31" t="s">
         <v>82</v>
       </c>
-      <c r="C31" t="s">
-        <v>46</v>
-      </c>
-      <c r="D31" t="s">
+      <c r="F31" t="s">
+        <v>64</v>
+      </c>
+      <c r="K31" t="s">
         <v>83</v>
-      </c>
-      <c r="F31" t="s">
-        <v>65</v>
-      </c>
-      <c r="K31" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
@@ -2023,19 +2017,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
+        <v>84</v>
+      </c>
+      <c r="C32" t="s">
+        <v>45</v>
+      </c>
+      <c r="D32" t="s">
         <v>85</v>
       </c>
-      <c r="C32" t="s">
-        <v>46</v>
-      </c>
-      <c r="D32" t="s">
+      <c r="F32" t="s">
+        <v>64</v>
+      </c>
+      <c r="K32" t="s">
         <v>86</v>
-      </c>
-      <c r="F32" t="s">
-        <v>65</v>
-      </c>
-      <c r="K32" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -2043,19 +2037,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
+        <v>87</v>
+      </c>
+      <c r="C33" t="s">
+        <v>45</v>
+      </c>
+      <c r="D33" t="s">
         <v>88</v>
       </c>
-      <c r="C33" t="s">
-        <v>46</v>
-      </c>
-      <c r="D33" t="s">
+      <c r="F33" t="s">
+        <v>64</v>
+      </c>
+      <c r="K33" t="s">
         <v>89</v>
-      </c>
-      <c r="F33" t="s">
-        <v>65</v>
-      </c>
-      <c r="K33" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
@@ -2063,19 +2057,19 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
+        <v>90</v>
+      </c>
+      <c r="C34" t="s">
+        <v>45</v>
+      </c>
+      <c r="D34" t="s">
         <v>91</v>
       </c>
-      <c r="C34" t="s">
-        <v>46</v>
-      </c>
-      <c r="D34" t="s">
+      <c r="F34" t="s">
+        <v>64</v>
+      </c>
+      <c r="K34" t="s">
         <v>92</v>
-      </c>
-      <c r="F34" t="s">
-        <v>65</v>
-      </c>
-      <c r="K34" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
@@ -2083,19 +2077,19 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
+        <v>93</v>
+      </c>
+      <c r="C35" t="s">
+        <v>45</v>
+      </c>
+      <c r="D35" t="s">
         <v>94</v>
       </c>
-      <c r="C35" t="s">
-        <v>46</v>
-      </c>
-      <c r="D35" t="s">
+      <c r="F35" t="s">
+        <v>64</v>
+      </c>
+      <c r="K35" t="s">
         <v>95</v>
-      </c>
-      <c r="F35" t="s">
-        <v>65</v>
-      </c>
-      <c r="K35" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -2103,16 +2097,16 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
+        <v>96</v>
+      </c>
+      <c r="C36" t="s">
+        <v>45</v>
+      </c>
+      <c r="D36" t="s">
         <v>97</v>
       </c>
-      <c r="C36" t="s">
-        <v>46</v>
-      </c>
-      <c r="D36" t="s">
-        <v>98</v>
-      </c>
       <c r="F36" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
@@ -2120,13 +2114,13 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
+        <v>98</v>
+      </c>
+      <c r="C37" t="s">
         <v>99</v>
       </c>
-      <c r="C37" t="s">
-        <v>100</v>
-      </c>
       <c r="F37" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
@@ -2134,19 +2128,19 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
+        <v>100</v>
+      </c>
+      <c r="C38" t="s">
+        <v>99</v>
+      </c>
+      <c r="D38" t="s">
         <v>101</v>
       </c>
-      <c r="C38" t="s">
-        <v>100</v>
-      </c>
-      <c r="D38" t="s">
+      <c r="F38" t="s">
         <v>102</v>
       </c>
-      <c r="F38" t="s">
+      <c r="J38" t="s">
         <v>103</v>
-      </c>
-      <c r="J38" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
@@ -2154,22 +2148,22 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
+        <v>104</v>
+      </c>
+      <c r="C39" t="s">
+        <v>99</v>
+      </c>
+      <c r="D39" t="s">
+        <v>101</v>
+      </c>
+      <c r="F39" t="s">
         <v>105</v>
       </c>
-      <c r="C39" t="s">
-        <v>100</v>
-      </c>
-      <c r="D39" t="s">
-        <v>102</v>
-      </c>
-      <c r="F39" t="s">
+      <c r="G39" t="s">
         <v>106</v>
       </c>
-      <c r="G39" t="s">
+      <c r="H39" t="s">
         <v>107</v>
-      </c>
-      <c r="H39" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
@@ -2177,16 +2171,16 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
+        <v>108</v>
+      </c>
+      <c r="C40" t="s">
+        <v>99</v>
+      </c>
+      <c r="D40" t="s">
         <v>109</v>
       </c>
-      <c r="C40" t="s">
-        <v>100</v>
-      </c>
-      <c r="D40" t="s">
-        <v>110</v>
-      </c>
       <c r="F40" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
@@ -2194,10 +2188,10 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F41" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J41">
         <v>1</v>
@@ -2208,16 +2202,16 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C42" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D42" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F42" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
@@ -2225,13 +2219,13 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C43" t="s">
+        <v>18</v>
+      </c>
+      <c r="F43" t="s">
         <v>19</v>
-      </c>
-      <c r="F43" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
@@ -2239,19 +2233,19 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
+        <v>113</v>
+      </c>
+      <c r="C44" t="s">
+        <v>18</v>
+      </c>
+      <c r="D44" t="s">
         <v>114</v>
       </c>
-      <c r="C44" t="s">
-        <v>19</v>
-      </c>
-      <c r="D44" t="s">
-        <v>115</v>
-      </c>
       <c r="F44" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J44" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
@@ -2259,16 +2253,16 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C45" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D45" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F45" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
@@ -2276,13 +2270,13 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
+        <v>116</v>
+      </c>
+      <c r="C46" t="s">
         <v>117</v>
       </c>
-      <c r="C46" t="s">
-        <v>118</v>
-      </c>
       <c r="F46" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
@@ -2290,16 +2284,16 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
+        <v>118</v>
+      </c>
+      <c r="C47" t="s">
+        <v>117</v>
+      </c>
+      <c r="D47" t="s">
         <v>119</v>
       </c>
-      <c r="C47" t="s">
-        <v>118</v>
-      </c>
-      <c r="D47" t="s">
-        <v>120</v>
-      </c>
       <c r="F47" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
@@ -2307,13 +2301,13 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
+        <v>120</v>
+      </c>
+      <c r="C48" t="s">
         <v>121</v>
       </c>
-      <c r="C48" t="s">
-        <v>122</v>
-      </c>
       <c r="F48" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
@@ -2321,22 +2315,22 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
+        <v>122</v>
+      </c>
+      <c r="C49" t="s">
+        <v>121</v>
+      </c>
+      <c r="D49" t="s">
         <v>123</v>
       </c>
-      <c r="C49" t="s">
-        <v>122</v>
-      </c>
-      <c r="D49" t="s">
+      <c r="F49" t="s">
+        <v>105</v>
+      </c>
+      <c r="G49" t="s">
         <v>124</v>
       </c>
-      <c r="F49" t="s">
-        <v>106</v>
-      </c>
-      <c r="G49" t="s">
+      <c r="H49" t="s">
         <v>125</v>
-      </c>
-      <c r="H49" t="s">
-        <v>126</v>
       </c>
       <c r="J49" t="b">
         <v>1</v>
@@ -2347,10 +2341,10 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F50" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J50">
         <v>1</v>
@@ -2361,16 +2355,16 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
+        <v>127</v>
+      </c>
+      <c r="C51" t="s">
+        <v>121</v>
+      </c>
+      <c r="D51" t="s">
         <v>128</v>
       </c>
-      <c r="C51" t="s">
-        <v>122</v>
-      </c>
-      <c r="D51" t="s">
-        <v>129</v>
-      </c>
       <c r="F51" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
@@ -2378,13 +2372,13 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
+        <v>129</v>
+      </c>
+      <c r="C52" t="s">
         <v>130</v>
       </c>
-      <c r="C52" t="s">
-        <v>131</v>
-      </c>
       <c r="F52" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
@@ -2392,16 +2386,16 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
+        <v>131</v>
+      </c>
+      <c r="C53" t="s">
+        <v>130</v>
+      </c>
+      <c r="D53" t="s">
         <v>132</v>
       </c>
-      <c r="C53" t="s">
-        <v>131</v>
-      </c>
-      <c r="D53" t="s">
-        <v>133</v>
-      </c>
       <c r="F53" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
@@ -2409,13 +2403,13 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
+        <v>133</v>
+      </c>
+      <c r="C54" t="s">
         <v>134</v>
       </c>
-      <c r="C54" t="s">
-        <v>135</v>
-      </c>
       <c r="F54" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
@@ -2423,16 +2417,16 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
+        <v>135</v>
+      </c>
+      <c r="C55" t="s">
+        <v>134</v>
+      </c>
+      <c r="D55" t="s">
         <v>136</v>
       </c>
-      <c r="C55" t="s">
-        <v>135</v>
-      </c>
-      <c r="D55" t="s">
-        <v>137</v>
-      </c>
       <c r="F55" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
@@ -2440,13 +2434,13 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
+        <v>137</v>
+      </c>
+      <c r="C56" t="s">
         <v>138</v>
       </c>
-      <c r="C56" t="s">
-        <v>139</v>
-      </c>
       <c r="F56" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
@@ -2454,19 +2448,19 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
+        <v>139</v>
+      </c>
+      <c r="C57" t="s">
+        <v>138</v>
+      </c>
+      <c r="D57" t="s">
         <v>140</v>
       </c>
-      <c r="C57" t="s">
-        <v>139</v>
-      </c>
-      <c r="D57" t="s">
+      <c r="F57" t="s">
+        <v>35</v>
+      </c>
+      <c r="K57" t="s">
         <v>141</v>
-      </c>
-      <c r="F57" t="s">
-        <v>36</v>
-      </c>
-      <c r="K57" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
@@ -2474,16 +2468,16 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
+        <v>142</v>
+      </c>
+      <c r="C58" t="s">
+        <v>138</v>
+      </c>
+      <c r="D58" t="s">
         <v>143</v>
       </c>
-      <c r="C58" t="s">
-        <v>139</v>
-      </c>
-      <c r="D58" t="s">
-        <v>144</v>
-      </c>
       <c r="F58" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
@@ -2491,13 +2485,13 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C59" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F59" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
@@ -2505,16 +2499,16 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
+        <v>145</v>
+      </c>
+      <c r="C60" t="s">
+        <v>138</v>
+      </c>
+      <c r="D60" t="s">
         <v>146</v>
       </c>
-      <c r="C60" t="s">
-        <v>139</v>
-      </c>
-      <c r="D60" t="s">
-        <v>147</v>
-      </c>
       <c r="F60" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
@@ -2522,16 +2516,16 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
+        <v>147</v>
+      </c>
+      <c r="C61" t="s">
+        <v>138</v>
+      </c>
+      <c r="D61" t="s">
         <v>148</v>
       </c>
-      <c r="C61" t="s">
-        <v>139</v>
-      </c>
-      <c r="D61" t="s">
-        <v>149</v>
-      </c>
       <c r="F61" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
@@ -2539,13 +2533,13 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C62" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F62" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
@@ -2553,16 +2547,16 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
+        <v>150</v>
+      </c>
+      <c r="C63" t="s">
+        <v>134</v>
+      </c>
+      <c r="D63" t="s">
         <v>151</v>
       </c>
-      <c r="C63" t="s">
-        <v>135</v>
-      </c>
-      <c r="D63" t="s">
-        <v>152</v>
-      </c>
       <c r="F63" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
@@ -2570,13 +2564,13 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C64" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F64" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
@@ -2584,22 +2578,22 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C65" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D65" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F65" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G65" t="s">
+        <v>124</v>
+      </c>
+      <c r="H65" t="s">
         <v>125</v>
-      </c>
-      <c r="H65" t="s">
-        <v>126</v>
       </c>
       <c r="J65" t="b">
         <v>1</v>
@@ -2610,10 +2604,10 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F66" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J66">
         <v>1</v>
@@ -2624,16 +2618,16 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
+        <v>155</v>
+      </c>
+      <c r="C67" t="s">
+        <v>121</v>
+      </c>
+      <c r="D67" t="s">
         <v>156</v>
       </c>
-      <c r="C67" t="s">
-        <v>122</v>
-      </c>
-      <c r="D67" t="s">
-        <v>157</v>
-      </c>
       <c r="F67" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
@@ -2641,13 +2635,13 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
+        <v>157</v>
+      </c>
+      <c r="C68" t="s">
         <v>158</v>
       </c>
-      <c r="C68" t="s">
-        <v>159</v>
-      </c>
       <c r="F68" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
@@ -2655,16 +2649,16 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
+        <v>159</v>
+      </c>
+      <c r="C69" t="s">
+        <v>158</v>
+      </c>
+      <c r="D69" t="s">
         <v>160</v>
       </c>
-      <c r="C69" t="s">
-        <v>159</v>
-      </c>
-      <c r="D69" t="s">
-        <v>161</v>
-      </c>
       <c r="F69" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
@@ -2672,13 +2666,13 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C70" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F70" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
@@ -2686,10 +2680,10 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F71" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J71">
         <v>1</v>
@@ -2700,16 +2694,16 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
+        <v>163</v>
+      </c>
+      <c r="C72" t="s">
+        <v>158</v>
+      </c>
+      <c r="D72" t="s">
         <v>164</v>
       </c>
-      <c r="C72" t="s">
-        <v>159</v>
-      </c>
-      <c r="D72" t="s">
-        <v>165</v>
-      </c>
       <c r="F72" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
@@ -2717,13 +2711,13 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
+        <v>165</v>
+      </c>
+      <c r="C73" t="s">
         <v>166</v>
       </c>
-      <c r="C73" t="s">
-        <v>167</v>
-      </c>
       <c r="F73" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
@@ -2731,19 +2725,19 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
+        <v>167</v>
+      </c>
+      <c r="C74" t="s">
+        <v>166</v>
+      </c>
+      <c r="D74" t="s">
         <v>168</v>
       </c>
-      <c r="C74" t="s">
-        <v>167</v>
-      </c>
-      <c r="D74" t="s">
+      <c r="F74" t="s">
+        <v>64</v>
+      </c>
+      <c r="K74" t="s">
         <v>169</v>
-      </c>
-      <c r="F74" t="s">
-        <v>65</v>
-      </c>
-      <c r="K74" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
@@ -2751,16 +2745,16 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
+        <v>170</v>
+      </c>
+      <c r="C75" t="s">
+        <v>166</v>
+      </c>
+      <c r="D75" t="s">
         <v>171</v>
       </c>
-      <c r="C75" t="s">
-        <v>167</v>
-      </c>
-      <c r="D75" t="s">
-        <v>172</v>
-      </c>
       <c r="F75" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
@@ -2768,19 +2762,19 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
+        <v>172</v>
+      </c>
+      <c r="C76" t="s">
+        <v>166</v>
+      </c>
+      <c r="D76" t="s">
+        <v>140</v>
+      </c>
+      <c r="F76" t="s">
+        <v>35</v>
+      </c>
+      <c r="K76" t="s">
         <v>173</v>
-      </c>
-      <c r="C76" t="s">
-        <v>167</v>
-      </c>
-      <c r="D76" t="s">
-        <v>141</v>
-      </c>
-      <c r="F76" t="s">
-        <v>36</v>
-      </c>
-      <c r="K76" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
@@ -2788,16 +2782,16 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C77" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D77" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F77" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
@@ -2805,13 +2799,13 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C78" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F78" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
@@ -2819,16 +2813,16 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
+        <v>176</v>
+      </c>
+      <c r="C79" t="s">
+        <v>166</v>
+      </c>
+      <c r="D79" t="s">
         <v>177</v>
       </c>
-      <c r="C79" t="s">
-        <v>167</v>
-      </c>
-      <c r="D79" t="s">
-        <v>178</v>
-      </c>
       <c r="F79" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
@@ -2836,16 +2830,16 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
+        <v>178</v>
+      </c>
+      <c r="C80" t="s">
+        <v>166</v>
+      </c>
+      <c r="D80" t="s">
         <v>179</v>
       </c>
-      <c r="C80" t="s">
-        <v>167</v>
-      </c>
-      <c r="D80" t="s">
-        <v>180</v>
-      </c>
       <c r="F80" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
@@ -2853,16 +2847,16 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
+        <v>180</v>
+      </c>
+      <c r="C81" t="s">
+        <v>166</v>
+      </c>
+      <c r="D81" t="s">
         <v>181</v>
       </c>
-      <c r="C81" t="s">
-        <v>167</v>
-      </c>
-      <c r="D81" t="s">
-        <v>182</v>
-      </c>
       <c r="F81" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
@@ -2870,13 +2864,13 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C82" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F82" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
@@ -2884,22 +2878,22 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C83" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D83" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F83" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G83" t="s">
+        <v>124</v>
+      </c>
+      <c r="H83" t="s">
         <v>125</v>
-      </c>
-      <c r="H83" t="s">
-        <v>126</v>
       </c>
       <c r="J83" t="b">
         <v>1</v>
@@ -2910,10 +2904,10 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F84" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J84">
         <v>1</v>
@@ -2924,16 +2918,16 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C85" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D85" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F85" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
@@ -2941,13 +2935,13 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
+        <v>165</v>
+      </c>
+      <c r="C86" t="s">
         <v>166</v>
       </c>
-      <c r="C86" t="s">
-        <v>167</v>
-      </c>
       <c r="F86" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
@@ -2955,19 +2949,19 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
+        <v>186</v>
+      </c>
+      <c r="C87" t="s">
+        <v>166</v>
+      </c>
+      <c r="D87" t="s">
+        <v>168</v>
+      </c>
+      <c r="F87" t="s">
+        <v>64</v>
+      </c>
+      <c r="K87" t="s">
         <v>187</v>
-      </c>
-      <c r="C87" t="s">
-        <v>167</v>
-      </c>
-      <c r="D87" t="s">
-        <v>169</v>
-      </c>
-      <c r="F87" t="s">
-        <v>65</v>
-      </c>
-      <c r="K87" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
@@ -2975,16 +2969,16 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C88" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D88" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F88" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
@@ -2992,19 +2986,19 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
+        <v>189</v>
+      </c>
+      <c r="C89" t="s">
+        <v>166</v>
+      </c>
+      <c r="D89" t="s">
+        <v>140</v>
+      </c>
+      <c r="F89" t="s">
+        <v>35</v>
+      </c>
+      <c r="K89" t="s">
         <v>190</v>
-      </c>
-      <c r="C89" t="s">
-        <v>167</v>
-      </c>
-      <c r="D89" t="s">
-        <v>141</v>
-      </c>
-      <c r="F89" t="s">
-        <v>36</v>
-      </c>
-      <c r="K89" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
@@ -3012,16 +3006,16 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C90" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D90" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F90" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
@@ -3029,13 +3023,13 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C91" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F91" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
@@ -3043,16 +3037,16 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C92" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D92" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F92" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
@@ -3060,16 +3054,16 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C93" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D93" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F93" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
@@ -3077,16 +3071,16 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C94" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D94" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F94" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
@@ -3094,13 +3088,13 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C95" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F95" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
@@ -3108,22 +3102,22 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C96" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D96" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F96" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G96" t="s">
+        <v>124</v>
+      </c>
+      <c r="H96" t="s">
         <v>125</v>
-      </c>
-      <c r="H96" t="s">
-        <v>126</v>
       </c>
       <c r="J96" t="b">
         <v>1</v>
@@ -3134,10 +3128,10 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F97" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J97">
         <v>1</v>
@@ -3148,16 +3142,16 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
+        <v>199</v>
+      </c>
+      <c r="C98" t="s">
+        <v>158</v>
+      </c>
+      <c r="D98" t="s">
+        <v>160</v>
+      </c>
+      <c r="F98" t="s">
         <v>200</v>
-      </c>
-      <c r="C98" t="s">
-        <v>159</v>
-      </c>
-      <c r="D98" t="s">
-        <v>161</v>
-      </c>
-      <c r="F98" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
@@ -3165,13 +3159,13 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C99" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F99" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
@@ -3179,16 +3173,16 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
+        <v>202</v>
+      </c>
+      <c r="C100" t="s">
         <v>203</v>
       </c>
-      <c r="C100" t="s">
+      <c r="D100" t="s">
         <v>204</v>
       </c>
-      <c r="D100" t="s">
-        <v>205</v>
-      </c>
       <c r="F100" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
@@ -3196,13 +3190,13 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
+        <v>205</v>
+      </c>
+      <c r="C101" t="s">
         <v>206</v>
       </c>
-      <c r="C101" t="s">
-        <v>207</v>
-      </c>
       <c r="F101" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
@@ -3210,22 +3204,22 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
+        <v>207</v>
+      </c>
+      <c r="C102" t="s">
+        <v>206</v>
+      </c>
+      <c r="D102" t="s">
         <v>208</v>
       </c>
-      <c r="C102" t="s">
-        <v>207</v>
-      </c>
-      <c r="D102" t="s">
-        <v>209</v>
-      </c>
       <c r="F102" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G102" t="s">
+        <v>124</v>
+      </c>
+      <c r="H102" t="s">
         <v>125</v>
-      </c>
-      <c r="H102" t="s">
-        <v>126</v>
       </c>
       <c r="J102" t="b">
         <v>1</v>
@@ -3236,16 +3230,16 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C103" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D103" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F103" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
@@ -3253,13 +3247,13 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C104" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F104" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
@@ -3267,10 +3261,10 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F105" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J105">
         <v>1</v>
@@ -3281,16 +3275,16 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
+        <v>212</v>
+      </c>
+      <c r="C106" t="s">
+        <v>158</v>
+      </c>
+      <c r="D106" t="s">
+        <v>160</v>
+      </c>
+      <c r="F106" t="s">
         <v>213</v>
-      </c>
-      <c r="C106" t="s">
-        <v>159</v>
-      </c>
-      <c r="D106" t="s">
-        <v>161</v>
-      </c>
-      <c r="F106" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
@@ -3298,13 +3292,13 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C107" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F107" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
@@ -3312,16 +3306,16 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
+        <v>215</v>
+      </c>
+      <c r="C108" t="s">
+        <v>166</v>
+      </c>
+      <c r="D108" t="s">
         <v>216</v>
       </c>
-      <c r="C108" t="s">
-        <v>167</v>
-      </c>
-      <c r="D108" t="s">
-        <v>217</v>
-      </c>
       <c r="F108" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
@@ -3329,13 +3323,13 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C109" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F109" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
@@ -3343,16 +3337,16 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
+        <v>218</v>
+      </c>
+      <c r="C110" t="s">
+        <v>206</v>
+      </c>
+      <c r="D110" t="s">
         <v>219</v>
       </c>
-      <c r="C110" t="s">
-        <v>207</v>
-      </c>
-      <c r="D110" t="s">
-        <v>220</v>
-      </c>
       <c r="F110" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
@@ -3360,16 +3354,16 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
+        <v>220</v>
+      </c>
+      <c r="C111" t="s">
+        <v>206</v>
+      </c>
+      <c r="D111" t="s">
         <v>221</v>
       </c>
-      <c r="C111" t="s">
-        <v>207</v>
-      </c>
-      <c r="D111" t="s">
-        <v>222</v>
-      </c>
       <c r="F111" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
@@ -3377,16 +3371,16 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C112" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D112" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F112" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
@@ -3394,13 +3388,13 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C113" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F113" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
@@ -3408,16 +3402,16 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C114" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D114" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F114" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
@@ -3425,13 +3419,13 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C115" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F115" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
@@ -3439,22 +3433,22 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C116" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D116" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F116" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G116" t="s">
+        <v>124</v>
+      </c>
+      <c r="H116" t="s">
         <v>125</v>
-      </c>
-      <c r="H116" t="s">
-        <v>126</v>
       </c>
       <c r="J116" t="b">
         <v>1</v>
@@ -3465,10 +3459,10 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F117" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J117">
         <v>1</v>
@@ -3479,16 +3473,16 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C118" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D118" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F118" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
@@ -3496,13 +3490,13 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C119" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F119" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
@@ -3510,16 +3504,16 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
+        <v>230</v>
+      </c>
+      <c r="C120" t="s">
+        <v>166</v>
+      </c>
+      <c r="D120" t="s">
         <v>231</v>
       </c>
-      <c r="C120" t="s">
-        <v>167</v>
-      </c>
-      <c r="D120" t="s">
-        <v>232</v>
-      </c>
       <c r="F120" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
@@ -3527,13 +3521,13 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C121" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F121" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.25">
@@ -3541,19 +3535,19 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
+        <v>233</v>
+      </c>
+      <c r="C122" t="s">
+        <v>166</v>
+      </c>
+      <c r="D122" t="s">
         <v>234</v>
       </c>
-      <c r="C122" t="s">
-        <v>167</v>
-      </c>
-      <c r="D122" t="s">
+      <c r="F122" t="s">
+        <v>64</v>
+      </c>
+      <c r="K122" t="s">
         <v>235</v>
-      </c>
-      <c r="F122" t="s">
-        <v>65</v>
-      </c>
-      <c r="K122" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.25">
@@ -3561,19 +3555,19 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
+        <v>236</v>
+      </c>
+      <c r="C123" t="s">
+        <v>166</v>
+      </c>
+      <c r="D123" t="s">
         <v>237</v>
       </c>
-      <c r="C123" t="s">
-        <v>167</v>
-      </c>
-      <c r="D123" t="s">
+      <c r="F123" t="s">
+        <v>64</v>
+      </c>
+      <c r="K123" t="s">
         <v>238</v>
-      </c>
-      <c r="F123" t="s">
-        <v>65</v>
-      </c>
-      <c r="K123" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.25">
@@ -3581,16 +3575,16 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C124" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D124" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F124" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.25">
@@ -3598,13 +3592,13 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C125" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F125" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.25">
@@ -3612,16 +3606,16 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
+        <v>241</v>
+      </c>
+      <c r="C126" t="s">
+        <v>158</v>
+      </c>
+      <c r="D126" t="s">
         <v>242</v>
       </c>
-      <c r="C126" t="s">
-        <v>159</v>
-      </c>
-      <c r="D126" t="s">
-        <v>243</v>
-      </c>
       <c r="F126" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.25">
@@ -3629,13 +3623,13 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C127" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F127" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.25">
@@ -3643,22 +3637,22 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C128" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D128" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F128" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G128" t="s">
+        <v>124</v>
+      </c>
+      <c r="H128" t="s">
         <v>125</v>
-      </c>
-      <c r="H128" t="s">
-        <v>126</v>
       </c>
       <c r="J128" t="b">
         <v>1</v>
@@ -3669,10 +3663,10 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="F129" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J129">
         <v>1</v>
@@ -3683,16 +3677,16 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C130" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D130" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F130" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.25">
@@ -3700,13 +3694,13 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C131" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F131" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.25">
@@ -3714,16 +3708,16 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
+        <v>247</v>
+      </c>
+      <c r="C132" t="s">
+        <v>203</v>
+      </c>
+      <c r="D132" t="s">
         <v>248</v>
       </c>
-      <c r="C132" t="s">
-        <v>204</v>
-      </c>
-      <c r="D132" t="s">
-        <v>249</v>
-      </c>
       <c r="F132" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.25">
@@ -3731,13 +3725,13 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
+        <v>249</v>
+      </c>
+      <c r="C133" t="s">
         <v>250</v>
       </c>
-      <c r="C133" t="s">
-        <v>251</v>
-      </c>
       <c r="F133" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.25">
@@ -3745,19 +3739,19 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
+        <v>251</v>
+      </c>
+      <c r="C134" t="s">
+        <v>250</v>
+      </c>
+      <c r="D134" t="s">
         <v>252</v>
       </c>
-      <c r="C134" t="s">
-        <v>251</v>
-      </c>
-      <c r="D134" t="s">
+      <c r="F134" t="s">
+        <v>64</v>
+      </c>
+      <c r="K134" t="s">
         <v>253</v>
-      </c>
-      <c r="F134" t="s">
-        <v>65</v>
-      </c>
-      <c r="K134" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.25">
@@ -3765,16 +3759,16 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C135" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D135" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F135" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.25">
@@ -3782,13 +3776,13 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C136" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F136" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.25">
@@ -3796,16 +3790,16 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C137" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D137" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F137" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.25">
@@ -3813,13 +3807,13 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C138" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F138" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.25">
@@ -3827,22 +3821,22 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C139" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D139" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F139" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G139" t="s">
+        <v>124</v>
+      </c>
+      <c r="H139" t="s">
         <v>125</v>
-      </c>
-      <c r="H139" t="s">
-        <v>126</v>
       </c>
       <c r="J139" t="b">
         <v>1</v>
@@ -3853,10 +3847,10 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="F140" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J140">
         <v>1</v>
@@ -3867,16 +3861,16 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C141" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D141" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F141" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.25">
@@ -3884,13 +3878,13 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F142" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.25">
@@ -3898,16 +3892,16 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C143" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D143" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F143" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.25">
@@ -3915,13 +3909,13 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C144" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F144" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.25">
@@ -3929,19 +3923,19 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
+        <v>263</v>
+      </c>
+      <c r="C145" t="s">
+        <v>166</v>
+      </c>
+      <c r="D145" t="s">
+        <v>234</v>
+      </c>
+      <c r="F145" t="s">
+        <v>64</v>
+      </c>
+      <c r="K145" t="s">
         <v>264</v>
-      </c>
-      <c r="C145" t="s">
-        <v>167</v>
-      </c>
-      <c r="D145" t="s">
-        <v>235</v>
-      </c>
-      <c r="F145" t="s">
-        <v>65</v>
-      </c>
-      <c r="K145" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.25">
@@ -3949,16 +3943,16 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C146" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D146" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F146" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.25">
@@ -3966,13 +3960,13 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="C147" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F147" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.25">
@@ -3980,16 +3974,16 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="C148" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D148" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F148" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.25">
@@ -3997,13 +3991,13 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C149" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F149" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="150" spans="1:11" x14ac:dyDescent="0.25">
@@ -4011,22 +4005,22 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C150" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D150" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F150" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G150" t="s">
+        <v>124</v>
+      </c>
+      <c r="H150" t="s">
         <v>125</v>
-      </c>
-      <c r="H150" t="s">
-        <v>126</v>
       </c>
       <c r="J150" t="b">
         <v>1</v>
@@ -4037,10 +4031,10 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="F151" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J151">
         <v>1</v>
@@ -4051,16 +4045,16 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
+        <v>271</v>
+      </c>
+      <c r="C152" t="s">
+        <v>18</v>
+      </c>
+      <c r="D152" t="s">
         <v>272</v>
       </c>
-      <c r="C152" t="s">
-        <v>19</v>
-      </c>
-      <c r="D152" t="s">
-        <v>273</v>
-      </c>
       <c r="F152" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="153" spans="1:11" x14ac:dyDescent="0.25">
@@ -4068,16 +4062,16 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
+        <v>273</v>
+      </c>
+      <c r="C153" t="s">
+        <v>18</v>
+      </c>
+      <c r="D153" t="s">
         <v>274</v>
       </c>
-      <c r="C153" t="s">
-        <v>19</v>
-      </c>
-      <c r="D153" t="s">
-        <v>275</v>
-      </c>
       <c r="F153" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="154" spans="1:11" x14ac:dyDescent="0.25">
@@ -4085,13 +4079,13 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C154" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F154" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -4130,84 +4124,84 @@
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>276</v>
+      </c>
+      <c r="B2" t="s">
         <v>277</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>278</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>279</v>
-      </c>
-      <c r="D2" t="s">
-        <v>280</v>
       </c>
       <c r="E2">
         <v>1234567890</v>
@@ -4216,52 +4210,52 @@
         <v>7700900000</v>
       </c>
       <c r="G2" t="s">
+        <v>280</v>
+      </c>
+      <c r="H2" t="s">
         <v>281</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
+        <v>279</v>
+      </c>
+      <c r="J2" t="s">
         <v>282</v>
       </c>
-      <c r="I2" t="s">
-        <v>280</v>
-      </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>283</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
+        <v>283</v>
+      </c>
+      <c r="M2" t="s">
         <v>284</v>
       </c>
-      <c r="L2" t="s">
-        <v>284</v>
-      </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>285</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>286</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>287</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
+        <v>286</v>
+      </c>
+      <c r="R2" t="s">
         <v>288</v>
       </c>
-      <c r="Q2" t="s">
-        <v>287</v>
-      </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
         <v>289</v>
       </c>
-      <c r="S2" t="s">
+      <c r="T2" t="s">
         <v>290</v>
       </c>
-      <c r="T2" t="s">
+      <c r="U2" t="s">
         <v>291</v>
       </c>
-      <c r="U2" t="s">
+      <c r="V2" t="s">
         <v>292</v>
-      </c>
-      <c r="V2" t="s">
-        <v>293</v>
       </c>
     </row>
   </sheetData>
@@ -4280,71 +4274,71 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>294</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>295</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>296</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>297</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>298</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>299</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>300</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>301</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>302</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>303</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>304</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>305</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>306</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>307</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>308</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B9" s="3">
         <v>153</v>
@@ -4352,7 +4346,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B10" s="3">
         <v>16</v>
@@ -4360,7 +4354,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B11" s="3">
         <v>55</v>
@@ -4368,15 +4362,15 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>312</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>313</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B13" s="4">
         <v>46147</v>
@@ -4384,7 +4378,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B14" s="4">
         <v>46147</v>
@@ -4392,31 +4386,31 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>316</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>317</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>318</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>319</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>320</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>321</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B18" s="3">
         <v>10</v>
@@ -4424,18 +4418,18 @@
     </row>
     <row r="19" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>323</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>324</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>325</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>326</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>327</v>
       </c>
     </row>
   </sheetData>
@@ -4455,71 +4449,77 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>328</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>302</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C2" t="s">
         <v>330</v>
-      </c>
-      <c r="C2" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B3" t="s">
+        <v>331</v>
+      </c>
+      <c r="C3" t="s">
         <v>332</v>
-      </c>
-      <c r="C3" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>333</v>
+      </c>
+      <c r="B4" t="s">
         <v>334</v>
       </c>
-      <c r="B4" t="s">
-        <v>335</v>
-      </c>
       <c r="C4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>335</v>
+      </c>
+      <c r="B5" t="s">
         <v>336</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>337</v>
-      </c>
-      <c r="C5" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>338</v>
+      </c>
+      <c r="B6" t="s">
         <v>339</v>
       </c>
-      <c r="B6" t="s">
-        <v>340</v>
-      </c>
       <c r="C6" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{a4153a30-97aa-49dd-8839-66f72081522c}" enabled="1" method="Standard" siteId="{9ffff5c3-bdfa-4a9d-b595-ff68329945ef}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>
--- a/lorenzo-playwright-kdf/excelFramework/testcases/Problems/LSTP_Problems_WF001.xlsx
+++ b/lorenzo-playwright-kdf/excelFramework/testcases/Problems/LSTP_Problems_WF001.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkrishnan6\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\Problems\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0567B2BB-0B8B-45CE-811E-262DE8705FDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{905BE72E-DA4A-419A-8669-AC9FD90CE48C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{BE3DF6D1-393A-4573-8176-869B7BDB99D6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="341">
   <si>
     <t>StepNo</t>
   </si>
@@ -1059,6 +1059,9 @@
   </si>
   <si>
     <t>Login password</t>
+  </si>
+  <si>
+    <t>launchRegistration</t>
   </si>
 </sst>
 </file>
@@ -2106,7 +2109,7 @@
         <v>97</v>
       </c>
       <c r="F36" t="s">
-        <v>24</v>
+        <v>340</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
@@ -2180,7 +2183,7 @@
         <v>109</v>
       </c>
       <c r="F40" t="s">
-        <v>24</v>
+        <v>340</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">

--- a/lorenzo-playwright-kdf/excelFramework/testcases/Problems/LSTP_Problems_WF001.xlsx
+++ b/lorenzo-playwright-kdf/excelFramework/testcases/Problems/LSTP_Problems_WF001.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bkrishnan6\ORBIS PAS UKI-LZO\lorenzo-playwright-kdf\excelFramework\testcases\Problems\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{905BE72E-DA4A-419A-8669-AC9FD90CE48C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB7147C3-6DC2-4896-914D-03A53AE691E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{BE3DF6D1-393A-4573-8176-869B7BDB99D6}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="340">
   <si>
     <t>StepNo</t>
   </si>
@@ -242,27 +242,18 @@
     <t>Enter Home Telephone number</t>
   </si>
   <si>
-    <t>txt_ TelephoneHome</t>
-  </si>
-  <si>
     <t>TELEPHONEHOME</t>
   </si>
   <si>
     <t>Enter Mobile Telephone number</t>
   </si>
   <si>
-    <t>txt_ TelephoneMobile</t>
-  </si>
-  <si>
     <t>TELEPHONEMOBILE</t>
   </si>
   <si>
     <t>Enter Email address</t>
   </si>
   <si>
-    <t>txt_ TelephoneEmail</t>
-  </si>
-  <si>
     <t>EMAIL</t>
   </si>
   <si>
@@ -650,9 +641,6 @@
     <t>Click Mark as Main Problem from context menu</t>
   </si>
   <si>
-    <t>page</t>
-  </si>
-  <si>
     <t>lnk_MarkasMainProblem</t>
   </si>
   <si>
@@ -1062,6 +1050,15 @@
   </si>
   <si>
     <t>launchRegistration</t>
+  </si>
+  <si>
+    <t>txt_TelephoneHome</t>
+  </si>
+  <si>
+    <t>txt_TelephoneMobile</t>
+  </si>
+  <si>
+    <t>txt_TelephoneEmail</t>
   </si>
 </sst>
 </file>
@@ -1895,13 +1892,13 @@
         <v>45</v>
       </c>
       <c r="D25" t="s">
-        <v>67</v>
+        <v>337</v>
       </c>
       <c r="F25" t="s">
         <v>35</v>
       </c>
       <c r="K25" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
@@ -1909,19 +1906,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C26" t="s">
         <v>45</v>
       </c>
       <c r="D26" t="s">
-        <v>70</v>
+        <v>338</v>
       </c>
       <c r="F26" t="s">
         <v>35</v>
       </c>
       <c r="K26" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
@@ -1929,19 +1926,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C27" t="s">
         <v>45</v>
       </c>
       <c r="D27" t="s">
-        <v>73</v>
+        <v>339</v>
       </c>
       <c r="F27" t="s">
         <v>35</v>
       </c>
       <c r="K27" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
@@ -1949,13 +1946,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C28" t="s">
         <v>45</v>
       </c>
       <c r="D28" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F28" t="s">
         <v>24</v>
@@ -1966,7 +1963,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C29" t="s">
         <v>45</v>
@@ -1980,19 +1977,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C30" t="s">
         <v>45</v>
       </c>
       <c r="D30" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F30" t="s">
         <v>64</v>
       </c>
       <c r="K30" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
@@ -2000,19 +1997,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C31" t="s">
         <v>45</v>
       </c>
       <c r="D31" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F31" t="s">
         <v>64</v>
       </c>
       <c r="K31" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
@@ -2020,19 +2017,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C32" t="s">
         <v>45</v>
       </c>
       <c r="D32" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F32" t="s">
         <v>64</v>
       </c>
       <c r="K32" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
@@ -2040,19 +2037,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C33" t="s">
         <v>45</v>
       </c>
       <c r="D33" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F33" t="s">
         <v>64</v>
       </c>
       <c r="K33" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
@@ -2060,19 +2057,19 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C34" t="s">
         <v>45</v>
       </c>
       <c r="D34" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F34" t="s">
         <v>64</v>
       </c>
       <c r="K34" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
@@ -2080,19 +2077,19 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C35" t="s">
         <v>45</v>
       </c>
       <c r="D35" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F35" t="s">
         <v>64</v>
       </c>
       <c r="K35" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -2100,16 +2097,16 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C36" t="s">
         <v>45</v>
       </c>
       <c r="D36" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F36" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
@@ -2117,10 +2114,10 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C37" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F37" t="s">
         <v>19</v>
@@ -2131,19 +2128,19 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
+        <v>97</v>
+      </c>
+      <c r="C38" t="s">
+        <v>18</v>
+      </c>
+      <c r="D38" t="s">
+        <v>98</v>
+      </c>
+      <c r="F38" t="s">
+        <v>99</v>
+      </c>
+      <c r="J38" t="s">
         <v>100</v>
-      </c>
-      <c r="C38" t="s">
-        <v>99</v>
-      </c>
-      <c r="D38" t="s">
-        <v>101</v>
-      </c>
-      <c r="F38" t="s">
-        <v>102</v>
-      </c>
-      <c r="J38" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
@@ -2151,22 +2148,22 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
+        <v>101</v>
+      </c>
+      <c r="C39" t="s">
+        <v>18</v>
+      </c>
+      <c r="D39" t="s">
+        <v>98</v>
+      </c>
+      <c r="F39" t="s">
+        <v>102</v>
+      </c>
+      <c r="G39" t="s">
+        <v>103</v>
+      </c>
+      <c r="H39" t="s">
         <v>104</v>
-      </c>
-      <c r="C39" t="s">
-        <v>99</v>
-      </c>
-      <c r="D39" t="s">
-        <v>101</v>
-      </c>
-      <c r="F39" t="s">
-        <v>105</v>
-      </c>
-      <c r="G39" t="s">
-        <v>106</v>
-      </c>
-      <c r="H39" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
@@ -2174,16 +2171,16 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C40" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D40" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F40" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
@@ -2191,7 +2188,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="F41" t="s">
         <v>21</v>
@@ -2205,7 +2202,7 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C42" t="s">
         <v>18</v>
@@ -2222,7 +2219,7 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C43" t="s">
         <v>18</v>
@@ -2236,19 +2233,19 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C44" t="s">
         <v>18</v>
       </c>
       <c r="D44" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F44" t="s">
         <v>35</v>
       </c>
       <c r="J44" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
@@ -2256,7 +2253,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C45" t="s">
         <v>18</v>
@@ -2273,10 +2270,10 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C46" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="F46" t="s">
         <v>19</v>
@@ -2287,13 +2284,13 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C47" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D47" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F47" t="s">
         <v>24</v>
@@ -2304,10 +2301,10 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C48" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F48" t="s">
         <v>19</v>
@@ -2318,22 +2315,22 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
+        <v>119</v>
+      </c>
+      <c r="C49" t="s">
+        <v>118</v>
+      </c>
+      <c r="D49" t="s">
+        <v>120</v>
+      </c>
+      <c r="F49" t="s">
+        <v>102</v>
+      </c>
+      <c r="G49" t="s">
+        <v>121</v>
+      </c>
+      <c r="H49" t="s">
         <v>122</v>
-      </c>
-      <c r="C49" t="s">
-        <v>121</v>
-      </c>
-      <c r="D49" t="s">
-        <v>123</v>
-      </c>
-      <c r="F49" t="s">
-        <v>105</v>
-      </c>
-      <c r="G49" t="s">
-        <v>124</v>
-      </c>
-      <c r="H49" t="s">
-        <v>125</v>
       </c>
       <c r="J49" t="b">
         <v>1</v>
@@ -2344,7 +2341,7 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F50" t="s">
         <v>21</v>
@@ -2358,13 +2355,13 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C51" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D51" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F51" t="s">
         <v>24</v>
@@ -2375,10 +2372,10 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C52" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F52" t="s">
         <v>19</v>
@@ -2389,13 +2386,13 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C53" t="s">
-        <v>130</v>
+        <v>18</v>
       </c>
       <c r="D53" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F53" t="s">
         <v>24</v>
@@ -2406,10 +2403,10 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C54" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F54" t="s">
         <v>19</v>
@@ -2420,13 +2417,13 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="C55" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D55" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F55" t="s">
         <v>24</v>
@@ -2437,10 +2434,10 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C56" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F56" t="s">
         <v>19</v>
@@ -2451,19 +2448,19 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C57" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D57" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F57" t="s">
         <v>35</v>
       </c>
       <c r="K57" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
@@ -2471,13 +2468,13 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C58" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D58" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F58" t="s">
         <v>24</v>
@@ -2488,10 +2485,10 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C59" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F59" t="s">
         <v>19</v>
@@ -2502,13 +2499,13 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C60" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D60" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F60" t="s">
         <v>24</v>
@@ -2519,13 +2516,13 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C61" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D61" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F61" t="s">
         <v>24</v>
@@ -2536,10 +2533,10 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C62" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F62" t="s">
         <v>19</v>
@@ -2550,13 +2547,13 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C63" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D63" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="F63" t="s">
         <v>24</v>
@@ -2567,10 +2564,10 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C64" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F64" t="s">
         <v>19</v>
@@ -2581,22 +2578,22 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C65" t="s">
+        <v>118</v>
+      </c>
+      <c r="D65" t="s">
+        <v>125</v>
+      </c>
+      <c r="F65" t="s">
+        <v>102</v>
+      </c>
+      <c r="G65" t="s">
         <v>121</v>
       </c>
-      <c r="D65" t="s">
-        <v>128</v>
-      </c>
-      <c r="F65" t="s">
-        <v>105</v>
-      </c>
-      <c r="G65" t="s">
-        <v>124</v>
-      </c>
       <c r="H65" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="J65" t="b">
         <v>1</v>
@@ -2607,7 +2604,7 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F66" t="s">
         <v>21</v>
@@ -2621,13 +2618,13 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C67" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D67" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="F67" t="s">
         <v>24</v>
@@ -2638,10 +2635,10 @@
         <v>67</v>
       </c>
       <c r="B68" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C68" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F68" t="s">
         <v>19</v>
@@ -2652,13 +2649,13 @@
         <v>68</v>
       </c>
       <c r="B69" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C69" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D69" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F69" t="s">
         <v>24</v>
@@ -2669,10 +2666,10 @@
         <v>69</v>
       </c>
       <c r="B70" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C70" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F70" t="s">
         <v>19</v>
@@ -2683,7 +2680,7 @@
         <v>70</v>
       </c>
       <c r="B71" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="F71" t="s">
         <v>21</v>
@@ -2697,13 +2694,13 @@
         <v>71</v>
       </c>
       <c r="B72" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C72" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D72" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F72" t="s">
         <v>24</v>
@@ -2714,10 +2711,10 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C73" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F73" t="s">
         <v>19</v>
@@ -2728,19 +2725,19 @@
         <v>73</v>
       </c>
       <c r="B74" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C74" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D74" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="F74" t="s">
         <v>64</v>
       </c>
       <c r="K74" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
@@ -2748,13 +2745,13 @@
         <v>74</v>
       </c>
       <c r="B75" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C75" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D75" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="F75" t="s">
         <v>24</v>
@@ -2765,19 +2762,19 @@
         <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C76" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D76" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F76" t="s">
         <v>35</v>
       </c>
       <c r="K76" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
@@ -2785,13 +2782,13 @@
         <v>76</v>
       </c>
       <c r="B77" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C77" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D77" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F77" t="s">
         <v>24</v>
@@ -2802,10 +2799,10 @@
         <v>77</v>
       </c>
       <c r="B78" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C78" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F78" t="s">
         <v>19</v>
@@ -2816,13 +2813,13 @@
         <v>78</v>
       </c>
       <c r="B79" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C79" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D79" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="F79" t="s">
         <v>24</v>
@@ -2833,13 +2830,13 @@
         <v>79</v>
       </c>
       <c r="B80" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C80" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D80" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="F80" t="s">
         <v>24</v>
@@ -2850,13 +2847,13 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C81" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D81" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="F81" t="s">
         <v>24</v>
@@ -2867,10 +2864,10 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="C82" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F82" t="s">
         <v>19</v>
@@ -2881,22 +2878,22 @@
         <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C83" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D83" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F83" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G83" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="H83" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="J83" t="b">
         <v>1</v>
@@ -2907,7 +2904,7 @@
         <v>83</v>
       </c>
       <c r="B84" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="F84" t="s">
         <v>21</v>
@@ -2921,13 +2918,13 @@
         <v>84</v>
       </c>
       <c r="B85" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C85" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D85" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F85" t="s">
         <v>24</v>
@@ -2938,10 +2935,10 @@
         <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C86" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F86" t="s">
         <v>19</v>
@@ -2952,19 +2949,19 @@
         <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C87" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D87" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="F87" t="s">
         <v>64</v>
       </c>
       <c r="K87" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
@@ -2972,13 +2969,13 @@
         <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C88" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D88" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="F88" t="s">
         <v>24</v>
@@ -2989,19 +2986,19 @@
         <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C89" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D89" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F89" t="s">
         <v>35</v>
       </c>
       <c r="K89" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
@@ -3009,13 +3006,13 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C90" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D90" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F90" t="s">
         <v>24</v>
@@ -3026,10 +3023,10 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C91" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F91" t="s">
         <v>19</v>
@@ -3040,13 +3037,13 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C92" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D92" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="F92" t="s">
         <v>24</v>
@@ -3057,13 +3054,13 @@
         <v>92</v>
       </c>
       <c r="B93" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="C93" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D93" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="F93" t="s">
         <v>24</v>
@@ -3074,13 +3071,13 @@
         <v>93</v>
       </c>
       <c r="B94" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C94" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D94" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="F94" t="s">
         <v>24</v>
@@ -3091,10 +3088,10 @@
         <v>94</v>
       </c>
       <c r="B95" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C95" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F95" t="s">
         <v>19</v>
@@ -3105,22 +3102,22 @@
         <v>95</v>
       </c>
       <c r="B96" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C96" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D96" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F96" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G96" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="H96" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="J96" t="b">
         <v>1</v>
@@ -3131,7 +3128,7 @@
         <v>96</v>
       </c>
       <c r="B97" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="F97" t="s">
         <v>21</v>
@@ -3145,16 +3142,16 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C98" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D98" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F98" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
@@ -3162,10 +3159,10 @@
         <v>98</v>
       </c>
       <c r="B99" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C99" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F99" t="s">
         <v>19</v>
@@ -3176,13 +3173,13 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C100" t="s">
-        <v>203</v>
+        <v>18</v>
       </c>
       <c r="D100" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="F100" t="s">
         <v>24</v>
@@ -3193,10 +3190,10 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C101" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="F101" t="s">
         <v>19</v>
@@ -3207,22 +3204,22 @@
         <v>101</v>
       </c>
       <c r="B102" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="C102" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D102" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="F102" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G102" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="H102" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="J102" t="b">
         <v>1</v>
@@ -3233,13 +3230,13 @@
         <v>102</v>
       </c>
       <c r="B103" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="C103" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D103" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="F103" t="s">
         <v>24</v>
@@ -3250,10 +3247,10 @@
         <v>103</v>
       </c>
       <c r="B104" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C104" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F104" t="s">
         <v>19</v>
@@ -3264,7 +3261,7 @@
         <v>104</v>
       </c>
       <c r="B105" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="F105" t="s">
         <v>21</v>
@@ -3278,16 +3275,16 @@
         <v>105</v>
       </c>
       <c r="B106" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="C106" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D106" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F106" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
@@ -3295,10 +3292,10 @@
         <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="C107" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F107" t="s">
         <v>19</v>
@@ -3309,13 +3306,13 @@
         <v>107</v>
       </c>
       <c r="B108" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C108" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D108" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="F108" t="s">
         <v>24</v>
@@ -3326,10 +3323,10 @@
         <v>108</v>
       </c>
       <c r="B109" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="C109" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="F109" t="s">
         <v>19</v>
@@ -3340,13 +3337,13 @@
         <v>109</v>
       </c>
       <c r="B110" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="C110" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D110" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="F110" t="s">
         <v>24</v>
@@ -3357,13 +3354,13 @@
         <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="C111" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D111" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="F111" t="s">
         <v>24</v>
@@ -3374,13 +3371,13 @@
         <v>111</v>
       </c>
       <c r="B112" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="C112" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D112" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="F112" t="s">
         <v>24</v>
@@ -3391,10 +3388,10 @@
         <v>112</v>
       </c>
       <c r="B113" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="C113" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F113" t="s">
         <v>19</v>
@@ -3405,13 +3402,13 @@
         <v>113</v>
       </c>
       <c r="B114" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C114" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D114" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="F114" t="s">
         <v>24</v>
@@ -3422,10 +3419,10 @@
         <v>114</v>
       </c>
       <c r="B115" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C115" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F115" t="s">
         <v>19</v>
@@ -3436,22 +3433,22 @@
         <v>115</v>
       </c>
       <c r="B116" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="C116" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D116" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F116" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G116" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="H116" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="J116" t="b">
         <v>1</v>
@@ -3462,7 +3459,7 @@
         <v>116</v>
       </c>
       <c r="B117" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="F117" t="s">
         <v>21</v>
@@ -3476,16 +3473,16 @@
         <v>117</v>
       </c>
       <c r="B118" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C118" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D118" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F118" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
@@ -3493,10 +3490,10 @@
         <v>118</v>
       </c>
       <c r="B119" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C119" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F119" t="s">
         <v>19</v>
@@ -3507,13 +3504,13 @@
         <v>119</v>
       </c>
       <c r="B120" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="C120" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D120" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="F120" t="s">
         <v>24</v>
@@ -3524,10 +3521,10 @@
         <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C121" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F121" t="s">
         <v>19</v>
@@ -3538,19 +3535,19 @@
         <v>121</v>
       </c>
       <c r="B122" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="C122" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D122" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="F122" t="s">
         <v>64</v>
       </c>
       <c r="K122" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.25">
@@ -3558,19 +3555,19 @@
         <v>122</v>
       </c>
       <c r="B123" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="C123" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D123" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="F123" t="s">
         <v>64</v>
       </c>
       <c r="K123" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.25">
@@ -3578,13 +3575,13 @@
         <v>123</v>
       </c>
       <c r="B124" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C124" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D124" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="F124" t="s">
         <v>24</v>
@@ -3595,10 +3592,10 @@
         <v>124</v>
       </c>
       <c r="B125" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="C125" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F125" t="s">
         <v>19</v>
@@ -3609,13 +3606,13 @@
         <v>125</v>
       </c>
       <c r="B126" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C126" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D126" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="F126" t="s">
         <v>24</v>
@@ -3626,10 +3623,10 @@
         <v>126</v>
       </c>
       <c r="B127" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C127" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F127" t="s">
         <v>19</v>
@@ -3640,22 +3637,22 @@
         <v>127</v>
       </c>
       <c r="B128" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="C128" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D128" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="F128" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G128" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="H128" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="J128" t="b">
         <v>1</v>
@@ -3666,7 +3663,7 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="F129" t="s">
         <v>21</v>
@@ -3680,16 +3677,16 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="C130" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D130" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F130" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.25">
@@ -3697,10 +3694,10 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C131" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F131" t="s">
         <v>19</v>
@@ -3711,13 +3708,13 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C132" t="s">
-        <v>203</v>
+        <v>18</v>
       </c>
       <c r="D132" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="F132" t="s">
         <v>24</v>
@@ -3728,10 +3725,10 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="C133" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="F133" t="s">
         <v>19</v>
@@ -3742,19 +3739,19 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="C134" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="D134" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="F134" t="s">
         <v>64</v>
       </c>
       <c r="K134" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.25">
@@ -3762,13 +3759,13 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="C135" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="D135" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F135" t="s">
         <v>24</v>
@@ -3779,10 +3776,10 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="C136" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="F136" t="s">
         <v>19</v>
@@ -3793,13 +3790,13 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="C137" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="D137" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F137" t="s">
         <v>24</v>
@@ -3810,10 +3807,10 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="C138" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F138" t="s">
         <v>19</v>
@@ -3824,22 +3821,22 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C139" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D139" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F139" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G139" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="H139" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="J139" t="b">
         <v>1</v>
@@ -3850,7 +3847,7 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="F140" t="s">
         <v>21</v>
@@ -3864,16 +3861,16 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C141" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D141" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F141" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.25">
@@ -3881,10 +3878,10 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="C142" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F142" t="s">
         <v>19</v>
@@ -3895,13 +3892,13 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C143" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D143" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="F143" t="s">
         <v>24</v>
@@ -3912,10 +3909,10 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C144" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F144" t="s">
         <v>19</v>
@@ -3926,19 +3923,19 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="C145" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D145" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="F145" t="s">
         <v>64</v>
       </c>
       <c r="K145" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.25">
@@ -3946,13 +3943,13 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="C146" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="D146" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="F146" t="s">
         <v>24</v>
@@ -3963,10 +3960,10 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C147" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F147" t="s">
         <v>19</v>
@@ -3977,13 +3974,13 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D148" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="F148" t="s">
         <v>24</v>
@@ -3994,10 +3991,10 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="C149" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F149" t="s">
         <v>19</v>
@@ -4008,22 +4005,22 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="C150" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D150" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="F150" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="G150" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="H150" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="J150" t="b">
         <v>1</v>
@@ -4034,7 +4031,7 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="F151" t="s">
         <v>21</v>
@@ -4048,13 +4045,13 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="C152" t="s">
         <v>18</v>
       </c>
       <c r="D152" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="F152" t="s">
         <v>24</v>
@@ -4065,13 +4062,13 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C153" t="s">
         <v>18</v>
       </c>
       <c r="D153" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F153" t="s">
         <v>24</v>
@@ -4082,7 +4079,7 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C154" t="s">
         <v>14</v>
@@ -4139,72 +4136,72 @@
         <v>65</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>74</v>
-      </c>
       <c r="H1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>95</v>
-      </c>
       <c r="N1" s="1" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="Q1" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="R1" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="R1" s="1" t="s">
-        <v>190</v>
-      </c>
       <c r="S1" s="1" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="B2" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="C2" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="D2" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="E2">
         <v>1234567890</v>
@@ -4213,52 +4210,52 @@
         <v>7700900000</v>
       </c>
       <c r="G2" t="s">
+        <v>276</v>
+      </c>
+      <c r="H2" t="s">
+        <v>277</v>
+      </c>
+      <c r="I2" t="s">
+        <v>275</v>
+      </c>
+      <c r="J2" t="s">
+        <v>278</v>
+      </c>
+      <c r="K2" t="s">
+        <v>279</v>
+      </c>
+      <c r="L2" t="s">
+        <v>279</v>
+      </c>
+      <c r="M2" t="s">
         <v>280</v>
       </c>
-      <c r="H2" t="s">
+      <c r="N2" t="s">
         <v>281</v>
       </c>
-      <c r="I2" t="s">
-        <v>279</v>
-      </c>
-      <c r="J2" t="s">
+      <c r="O2" t="s">
         <v>282</v>
       </c>
-      <c r="K2" t="s">
+      <c r="P2" t="s">
         <v>283</v>
       </c>
-      <c r="L2" t="s">
-        <v>283</v>
-      </c>
-      <c r="M2" t="s">
+      <c r="Q2" t="s">
+        <v>282</v>
+      </c>
+      <c r="R2" t="s">
         <v>284</v>
       </c>
-      <c r="N2" t="s">
+      <c r="S2" t="s">
         <v>285</v>
       </c>
-      <c r="O2" t="s">
+      <c r="T2" t="s">
         <v>286</v>
       </c>
-      <c r="P2" t="s">
+      <c r="U2" t="s">
         <v>287</v>
       </c>
-      <c r="Q2" t="s">
-        <v>286</v>
-      </c>
-      <c r="R2" t="s">
+      <c r="V2" t="s">
         <v>288</v>
-      </c>
-      <c r="S2" t="s">
-        <v>289</v>
-      </c>
-      <c r="T2" t="s">
-        <v>290</v>
-      </c>
-      <c r="U2" t="s">
-        <v>291</v>
-      </c>
-      <c r="V2" t="s">
-        <v>292</v>
       </c>
     </row>
   </sheetData>
@@ -4277,71 +4274,71 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="B9" s="3">
         <v>153</v>
@@ -4349,7 +4346,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="B10" s="3">
         <v>16</v>
@@ -4357,7 +4354,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="B11" s="3">
         <v>55</v>
@@ -4365,15 +4362,15 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="B13" s="4">
         <v>46147</v>
@@ -4381,7 +4378,7 @@
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="B14" s="4">
         <v>46147</v>
@@ -4389,31 +4386,31 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="60" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="B18" s="3">
         <v>10</v>
@@ -4421,18 +4418,18 @@
     </row>
     <row r="19" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
   </sheetData>
@@ -4452,13 +4449,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -4466,54 +4463,54 @@
         <v>36</v>
       </c>
       <c r="B2" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="C2" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B3" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C3" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="B4" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="C4" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="B5" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="C5" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="B6" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="C6" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
     </row>
   </sheetData>
